--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -900,108 +900,108 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Under Armour, Inc.</t>
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>42.2</v>
+        <v>40.8</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Under Armour, Inc.</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>42.1</v>
+        <v>38.8</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>39.6</v>
+        <v>33.7</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>4.9</v>
@@ -1044,26 +1044,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Charter Communications, In</t>
+          <t>Lindblad Expeditions Holdi</t>
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -1073,33 +1073,33 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdi</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>25.4</v>
+        <v>24</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -1116,26 +1116,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1145,33 +1145,33 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>HGV</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>FRP Holdings, Inc.</t>
+          <t>Hilton Grand Vacations Inc</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Leonard Potter</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1181,33 +1181,33 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>Charter Communications, In</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>22.9</v>
+        <v>21.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1217,33 +1217,33 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>HGV</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations Inc</t>
+          <t>FRP Holdings, Inc.</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Leonard Potter</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>2.6</v>
@@ -1332,26 +1332,26 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>LanzaTech Global, Inc.</t>
+          <t>Toll Brothers, Inc.</t>
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
@@ -1476,26 +1476,26 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1505,33 +1505,33 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Beazer Homes USA, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1541,33 +1541,33 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Beazer Homes USA, Inc.</t>
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
@@ -1620,26 +1620,26 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Toll Brothers, Inc.</t>
+          <t>QXO, Inc.</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -1649,33 +1649,33 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>QXO, Inc.</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -1685,38 +1685,38 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Everest Group, Ltd.</t>
+          <t>Affirm Holdings, Inc.</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Keith Rabois</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -1728,62 +1728,62 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Affirm Holdings, Inc.</t>
+          <t>SandRidge Energy, Inc.</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Keith Rabois</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>SandRidge Energy, Inc.</t>
+          <t>Westrock Coffee Company</t>
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>12.1</v>
+        <v>10</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -1793,33 +1793,33 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Westrock Coffee Company</t>
+          <t>Allogene Therapeutics, Inc</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -1829,33 +1829,33 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics, Inc</t>
+          <t>Coya Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -1872,36 +1872,36 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Coya Therapeutics, Inc.</t>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>1</v>
@@ -1980,98 +1980,98 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>LanzaTech Global, Inc.</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Agenus Inc.</t>
+          <t>TPG Inc.</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Ring Energy, Inc.</t>
+          <t>Ingevity Corporation</t>
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -2081,69 +2081,69 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>TPG Inc.</t>
+          <t>Ring Energy, Inc.</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Ingevity Corporation</t>
+          <t>Warner Music Group Corp.</t>
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>2</v>
@@ -2196,26 +2196,26 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Warner Music Group Corp.</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -2225,33 +2225,33 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Innoviva, Inc.</t>
+          <t>Agenus Inc.</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -2448,247 +2448,247 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Stratasys Ltd.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.5</v>
+        <v>6.2</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Sharmila Mulligan</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Stratasys Ltd.</t>
         </is>
       </c>
       <c r="C49" s="10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="C51" s="10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D51" s="10" t="n">
         <v>3.2</v>
-      </c>
-      <c r="D51" s="10" t="n">
-        <v>1.9</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
         <v>2.9</v>
       </c>
       <c r="D53" s="10" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Sharmila Mulligan</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t xml:space="preserve">Silicon Motion Technology </t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Steve Chen</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="C55" s="10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="D55" s="10" t="n">
         <v>1.3</v>
@@ -2736,26 +2736,26 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -2765,249 +2765,249 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Houlihan Lokey, Inc.</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Tommaso Lillo</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>Houlihan Lokey, Inc.</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Tommaso Lillo</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D62" s="10" t="n">
         <v>1</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>0.7</v>
       </c>
       <c r="E62" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -3017,69 +3017,69 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="D64" s="10" t="n">
-        <v>0.4</v>
-      </c>
       <c r="E64" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3089,110 +3089,110 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silicon Motion Technology </t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>Steve Chen</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>SASOF</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Sasol Limited</t>
+          <t>Star Bulk Carriers Corp.</t>
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Vuyo Kahla</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>SASOF</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Century Aluminum Company</t>
+          <t>Sasol Limited</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D68" s="10" t="n">
         <v>0.3</v>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>1.3</v>
       </c>
       <c r="E68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Vuyo Kahla</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
@@ -3204,26 +3204,26 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Century Aluminum Company</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E69" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -3233,19 +3233,19 @@
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Kenon Holdings Ltd.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -3269,33 +3269,33 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers Corp.</t>
+          <t>Kenon Holdings Ltd.</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D71" s="10" t="n">
         <v>0.1</v>
-      </c>
-      <c r="D71" s="10" t="n">
-        <v>1.7</v>
       </c>
       <c r="E71" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -3305,33 +3305,33 @@
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>ADDYY</t>
+          <t>WIT</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>adidas AG</t>
+          <t>Wipro Limited</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E72" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Nassef Sawiris</t>
+          <t>Rishad Premji</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -3341,19 +3341,19 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>UPMMY</t>
+          <t>ADDYY</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>UPM-Kymmene Oyj</t>
+          <t>adidas AG</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Henrik Ehrnrooth</t>
+          <t>Nassef Sawiris</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
@@ -3377,19 +3377,19 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>UPMMY</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>CK Hutchison Holdings Limi</t>
+          <t>UPM-Kymmene Oyj</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
@@ -3403,29 +3403,29 @@
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Kwai Wong</t>
+          <t>Henrik Ehrnrooth</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>0086.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited</t>
+          <t>CK Hutchison Holdings Limi</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Jacqueline Leung</t>
+          <t>Kwai Wong</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -3449,19 +3449,19 @@
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0086.HK</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Tencent Holdings Limited</t>
+          <t>Sun Hung Kai &amp; Co. Limited</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
@@ -3475,29 +3475,29 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Jacqueline Leung</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>360ONE.NS</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>360 One Wam Limited</t>
+          <t>Tencent Holdings Limited</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
@@ -3511,29 +3511,29 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Akhil Gupta</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network,Gulf/Roy</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>ABBN.SW</t>
+          <t>360ONE.NS</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>ABB Ltd</t>
+          <t>360 One Wam Limited</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
@@ -3547,43 +3547,43 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Jacob Wallenberg</t>
+          <t>Akhil Gupta</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Sequoia Network,Gulf/Roy</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>WIT</t>
+          <t>ABBN.SW</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Wipro Limited</t>
+          <t>ABB Ltd</t>
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Rishad Premji</t>
+          <t>Jacob Wallenberg</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C81" s="10" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="D81" s="10" t="n">
         <v>1.7</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>-7.1</v>
+        <v>-7.2</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>1.3</v>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>1</v>
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="G9" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -5907,61 +5907,61 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>42.2</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>42.1</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -5991,18 +5991,18 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Lindblad Expeditions Holding</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -6017,22 +6017,22 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>26.8</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holding</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -6077,22 +6077,22 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>25.4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -6107,22 +6107,22 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -6137,22 +6137,22 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Leonard Potter</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -6167,22 +6167,22 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>HGV</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -6197,22 +6197,22 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Leonard Potter</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -6227,11 +6227,11 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>HGV</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -6261,18 +6261,18 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -6287,11 +6287,11 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>19.4</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -6417,12 +6417,12 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
@@ -6447,12 +6447,12 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>David Wright</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Rezolve Ai</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -6462,27 +6462,27 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>RZLVW</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -6497,22 +6497,22 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>15.9</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Richard Russell</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>LM Funding America</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -6557,22 +6557,22 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>LMFA</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>15.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Servi</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -6587,17 +6587,17 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>15.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6681,13 +6681,13 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6741,18 +6741,18 @@
         </is>
       </c>
       <c r="F32" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -6767,22 +6767,22 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
-        <v>15</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>David Wright</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Rezolve Ai</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -6792,27 +6792,27 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>RZLVW</t>
         </is>
       </c>
       <c r="F34" s="10" t="n">
-        <v>15</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -6827,22 +6827,22 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F36" s="10" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Richard Russell</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>LM Funding America</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
@@ -6887,22 +6887,22 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>LMFA</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Uniti Group (Financial Servi</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -6917,11 +6917,11 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F38" s="10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6957,12 +6957,12 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -6977,22 +6977,22 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F40" s="10" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F42" s="10" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7077,12 +7077,12 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -7097,22 +7097,22 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Jonathan Frates</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F45" s="10" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Jonathan Frates</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7167,12 +7167,12 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -7257,12 +7257,12 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
@@ -7272,16 +7272,16 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F50" s="10" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="F51" s="10" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -7341,18 +7341,18 @@
         </is>
       </c>
       <c r="F52" s="10" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -7362,27 +7362,27 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F55" s="10" t="n">
@@ -7467,12 +7467,12 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -7487,11 +7487,11 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -7557,12 +7557,12 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -7577,52 +7577,52 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F60" s="10" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F61" s="10" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -7637,52 +7637,52 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F62" s="10" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F63" s="10" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -7697,22 +7697,22 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F64" s="10" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F65" s="10" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -7757,22 +7757,22 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -7787,22 +7787,22 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -7817,22 +7817,22 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F68" s="10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -7847,22 +7847,22 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
@@ -7887,12 +7887,12 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -7907,22 +7907,22 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -7932,16 +7932,16 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -8007,12 +8007,12 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -8027,22 +8027,22 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -8057,22 +8057,22 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -8087,11 +8087,11 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -8157,12 +8157,12 @@
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -8177,22 +8177,22 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -8207,22 +8207,22 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
@@ -8247,7 +8247,7 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8277,7 +8277,7 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8307,12 +8307,12 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -8327,22 +8327,22 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -8357,11 +8357,11 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -8397,12 +8397,12 @@
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>Phillip Kardis</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Stratasys (Printing Services</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -8442,22 +8442,22 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>Subramaniam Viswanathan</t>
+          <t>Phillip Kardis</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -8487,12 +8487,12 @@
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Subramaniam Viswanathan</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -8502,27 +8502,27 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -8532,27 +8532,27 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -8562,27 +8562,27 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -8597,22 +8597,22 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -8627,22 +8627,22 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -8657,22 +8657,22 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -8687,22 +8687,22 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -8717,17 +8717,17 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -8757,7 +8757,7 @@
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -8787,7 +8787,7 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -8817,7 +8817,7 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -8907,7 +8907,7 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -8967,12 +8967,12 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -8987,22 +8987,22 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F107" s="10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="F108" s="10" t="n">
@@ -9027,12 +9027,12 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -9042,27 +9042,27 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F109" s="10" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
@@ -9072,27 +9072,27 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F110" s="10" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>Jane O'Keeffe</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Bancroft Fund</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>BCV-PA</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F111" s="10" t="n">
@@ -9117,12 +9117,12 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Jane O'Keeffe</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Bancroft Fund</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -9137,22 +9137,22 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>BCV-PA</t>
         </is>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Chi-Tung Liu</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -9167,17 +9167,17 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F113" s="10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Chi-Tung Liu</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -9207,12 +9207,12 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -9227,22 +9227,22 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F115" s="10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>Vuyo Kahla</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Sasol</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -9252,27 +9252,27 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>SASOF</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F116" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Vuyo Kahla</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Century Aluminum</t>
+          <t>Sasol</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -9282,27 +9282,27 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>SASOF</t>
         </is>
       </c>
       <c r="F117" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Century Aluminum</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
@@ -9317,22 +9317,22 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="F118" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="F119" s="10" t="n">
@@ -9357,7 +9357,7 @@
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>Idan Ofer</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -9387,12 +9387,12 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Idan Ofer</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
@@ -9407,11 +9407,11 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F121" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="F123" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="F124" s="10" t="n">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="F125" s="10" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="F126" s="10" t="n">
-        <v>-7.1</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1020,7 +1020,7 @@
         <v>32.4</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         <v>21.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>1</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>1</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>1</v>
@@ -1836,26 +1836,26 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>COYA</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Coya Therapeutics, Inc.</t>
+          <t>GLRE</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -1863,81 +1863,81 @@
           <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>Coya Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>GLRE</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>UPWK</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>1</v>
@@ -2736,26 +2736,26 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
         <v>2.4</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -2765,33 +2765,33 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -2916,52 +2916,52 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="C61" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D61" s="10" t="n">
         <v>1.4</v>
       </c>
-      <c r="D61" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="E61" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>1</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -2981,69 +2981,69 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -3053,33 +3053,33 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E65" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
@@ -3089,43 +3089,43 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E83" s="10" t="n">
         <v>1</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -7347,12 +7347,12 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F53" s="10" t="n">
@@ -7377,12 +7377,12 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -7397,11 +7397,11 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -7827,12 +7827,12 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F69" s="10" t="n">
@@ -7857,12 +7857,12 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
@@ -7887,12 +7887,12 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -7902,16 +7902,16 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8667,12 +8667,12 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
@@ -8697,12 +8697,12 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -8717,11 +8717,11 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="F109" s="10" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -12084,7 +12084,7 @@
     <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="10.5" customWidth="1" min="3" max="3"/>
     <col width="10.5" customWidth="1" min="4" max="4"/>
-    <col width="24.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
     <col width="9.5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>TAIWAN SEMICONDUCTOR M</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="F10" s="11" t="n">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -17,11 +17,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'README'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Board Signal — In Universe'!$A$4:$H$84</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Board Signal — In Universe'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Investor Board Seats'!$A$4:$G$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Investor Board Seats'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Board Convergence'!$A$4:$G$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Board Convergence'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Watchlist — Not in Universe'!$A$4:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Watchlist — Not in Universe'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Family Office &amp; SWF Map'!$A$4:$F$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Family Office &amp; SWF Map'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Network Roster Adds'!$A$4:$F$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Network Roster Adds'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3778,6 +3784,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:H84"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -4762,6 +4769,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:G29"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5439,6 +5447,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:G22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -5825,6 +5834,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:D20"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -12061,6 +12071,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F204"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -12323,6 +12334,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -526,7 +526,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>People &amp; Board Tea-Leaves — Alpha Monitor</t>
@@ -839,7 +839,7 @@
     <col width="18.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Board Signal — connected directors on tradeable companies</t>
@@ -861,7 +861,7 @@
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>TICKER</t>
@@ -903,7 +903,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>UAA</t>
@@ -939,7 +939,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>RSG</t>
@@ -975,7 +975,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BX</t>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>RIG</t>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>LIND</t>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>MNRO</t>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>SLB</t>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>HGV</t>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>CHTR</t>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>FRPH</t>
@@ -1263,7 +1263,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>HTO</t>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>XMTR</t>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TOL</t>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>CMPS</t>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>VEON</t>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>DRIO</t>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>VMC</t>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>SANA</t>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>BZH</t>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="14" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>IAG</t>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="14" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>QXO</t>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>EG</t>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>AFRM</t>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>SD</t>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>WEST</t>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="14" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>ALLO</t>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>GLRE</t>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="14" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>COYA</t>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="14" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>UPWK</t>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>GBX</t>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>LNZA</t>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="14" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>TPG</t>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
+    <row r="37" ht="14" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>NGVT</t>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>REI</t>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>WMG</t>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>MP</t>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="14" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>INVA</t>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="14" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>AGEN</t>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>DFS.L</t>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>PMTR</t>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>ADAG</t>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>TDTH</t>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>SKF-B.ST</t>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>COP</t>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>SSYS</t>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>BSRR</t>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>TTE</t>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>LE</t>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>CMC</t>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>SIMO</t>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="14" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>PRCH</t>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>AMPX</t>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="14" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>SMTC</t>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="14" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
           <t>HLI</t>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
+    <row r="59" ht="14" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
           <t>HBR.L</t>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
+    <row r="60" ht="14" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
           <t>RLXXF</t>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
+    <row r="61" ht="14" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
           <t>UBSI</t>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
+    <row r="62" ht="14" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
           <t>DAC</t>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
           <t>EVR</t>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
           <t>VIV</t>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>WOPEF</t>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
+    <row r="66" ht="14" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
           <t>UMC</t>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67" ht="14" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
         <is>
           <t>SBLK</t>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
+    <row r="68" ht="14" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
         <is>
           <t>SASOF</t>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
+    <row r="69" ht="14" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
           <t>CENX</t>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
+    <row r="70" ht="14" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
           <t>EIPAF</t>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
+    <row r="71" ht="14" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
           <t>KEN</t>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
+    <row r="72" ht="14" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
           <t>WIT</t>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="14" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
         <is>
           <t>ADDYY</t>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
+    <row r="74" ht="14" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
           <t>UPMMY</t>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
+    <row r="75" ht="14" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
           <t>0001.HK</t>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
         <is>
           <t>0086.HK</t>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
+    <row r="77" ht="14" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
           <t>0700.HK</t>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
+    <row r="78" ht="14" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
         <is>
           <t>360ONE.NS</t>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
+    <row r="79" ht="14" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
         <is>
           <t>ABBN.SW</t>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
+    <row r="80" ht="14" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
         <is>
           <t>BLSH</t>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
         <is>
           <t>SFM</t>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
         <is>
           <t>GH</t>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
+    <row r="83" ht="14" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
         <is>
           <t>OKLO</t>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
+    <row r="84" ht="14" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
         <is>
           <t>BROS</t>
@@ -3813,7 +3813,7 @@
     <col width="24.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Investor Board Seats — the activism / involvement tell</t>
@@ -3834,7 +3834,7 @@
       <c r="G2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>DIRECTOR</t>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Yoav Shaked</t>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Keith Rabois</t>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Len Blavatnik</t>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Steve Chen</t>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Nassef Sawiris</t>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Jacob Wallenberg</t>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Alan Howard</t>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Alexey Marey</t>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Carl Bennet</t>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Hassan Ouriagli</t>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>James Parsons</t>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Khalid Al Rumaihi</t>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Lakshmi Mittal</t>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Mukesh Ambani</t>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Naguib Sawiris</t>
@@ -4398,7 +4398,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Naguib Sawiris</t>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Nathaniel Rothschild</t>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Nita Ambani</t>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Pansy Ho</t>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="14" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Soopakij Chearavanont</t>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="14" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Steve Chen</t>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Steve Chen</t>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Suphachai Chearavanont</t>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Zachary Sternberg</t>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Ravi Gupta</t>
@@ -4798,7 +4798,7 @@
     <col width="11.5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Board Convergence — where networks stack up</t>
@@ -4819,7 +4819,7 @@
       <c r="G2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>COMPANY</t>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>NOVATEK (Russia</t>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>En+ Group</t>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Bank Of South Carolina</t>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Vulcan Energy Resources</t>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Vulcan Materials</t>
@@ -5019,7 +5019,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Aston Martin Lagonda Global Ho</t>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Charoen Pokphand Foods</t>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>ERG</t>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Multiply Group PJSC</t>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Novatek Microelectronics</t>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Playtech</t>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Shamal Az-Zour Al-Oula</t>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Siam Cement Public Company</t>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Trident Lifeline</t>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Trident Tools</t>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Veon</t>
@@ -5380,7 +5380,7 @@
         <v>17.6</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Vulcan Industries (London</t>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Vulcan Steel (Industrial Suppl</t>
@@ -5473,7 +5473,7 @@
     <col width="30.5" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Board Signal — Not Yet in Our Universe</t>
@@ -5491,7 +5491,7 @@
       <c r="D2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>COMPANY</t>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>NOVATEK (Russia</t>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>En+ Group</t>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Vulcan Energy Resources</t>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Bank Of South Carolina</t>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Vulcan Steel (Industrial Supplies and Pa</t>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Vulcan Industries (London</t>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Trident Tools</t>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Trident Lifeline</t>
@@ -5673,7 +5673,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Siam Cement Public Company</t>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Shamal Az-Zour Al-Oula</t>
@@ -5713,7 +5713,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Playtech</t>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Novatek Microelectronics</t>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Multiply Group PJSC</t>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>ERG</t>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Charoen Pokphand Foods</t>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Aston Martin Lagonda Global Holdings</t>
@@ -5862,7 +5862,7 @@
     <col width="11.5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Family Office / Sovereign-Wealth Board Map</t>
@@ -5882,7 +5882,7 @@
       <c r="F2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>INDIVIDUAL</t>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Dawn Fitzpatrick</t>
@@ -5944,7 +5944,7 @@
         <v>40.8</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Viral Patel</t>
@@ -5974,7 +5974,7 @@
         <v>33.7</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Margareth Ovrum</t>
@@ -6004,7 +6004,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Pamala Kaufman</t>
@@ -6034,7 +6034,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Ashok Srivastava</t>
@@ -6064,7 +6064,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Hope Woodhouse</t>
@@ -6094,7 +6094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Tatiana Mitrova</t>
@@ -6124,7 +6124,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Ashwini Kumar</t>
@@ -6154,7 +6154,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Leonard Potter</t>
@@ -6184,7 +6184,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>W. Conn</t>
@@ -6214,7 +6214,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>John Baker</t>
@@ -6244,7 +6244,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Gregory Landis</t>
@@ -6274,7 +6274,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Derek Kan</t>
@@ -6304,7 +6304,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Annalisa Jenkins</t>
@@ -6334,7 +6334,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="14" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Andrew Crowley</t>
@@ -6364,7 +6364,7 @@
         <v>18.1</v>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Brandon Lewis</t>
@@ -6394,7 +6394,7 @@
         <v>17.6</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Duncan Perry</t>
@@ -6424,7 +6424,7 @@
         <v>17.6</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>C. Wes Burton</t>
@@ -6454,7 +6454,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Cynthia Hostetler</t>
@@ -6484,7 +6484,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
+    <row r="24" ht="14" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>David Clement</t>
@@ -6514,7 +6514,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="14" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Denson Franklin</t>
@@ -6544,7 +6544,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>George Willis</t>
@@ -6574,7 +6574,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>J. Hill</t>
@@ -6604,7 +6604,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>J. Thomas Hill</t>
@@ -6634,7 +6634,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Jerry Perkins</t>
@@ -6664,7 +6664,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="14" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Mark Warren</t>
@@ -6694,7 +6694,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="14" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Mary Carlisle</t>
@@ -6724,7 +6724,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="14" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Thomas Fanning</t>
@@ -6754,7 +6754,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="14" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Richard Mulligan</t>
@@ -6784,7 +6784,7 @@
         <v>16.6</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>David Wright</t>
@@ -6814,7 +6814,7 @@
         <v>16.4</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
+    <row r="35" ht="14" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Danny Shepherd</t>
@@ -6844,7 +6844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
+    <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Michael Insulan</t>
@@ -6874,7 +6874,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
+    <row r="37" ht="14" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Richard Russell</t>
@@ -6904,7 +6904,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Kenneth Gunderman</t>
@@ -6934,7 +6934,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Joseph Flaim</t>
@@ -6964,7 +6964,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Mary Kissel</t>
@@ -6994,7 +6994,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="14" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Meryl Hartzband</t>
@@ -7024,7 +7024,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="14" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Jonathan Christodoro</t>
@@ -7054,7 +7054,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Louis Pastor</t>
@@ -7084,7 +7084,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
           <t>James Nelson</t>
@@ -7114,7 +7114,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Jonathan Frates</t>
@@ -7144,7 +7144,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Nancy Dunlap</t>
@@ -7174,7 +7174,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Bill Roeschlein</t>
@@ -7204,7 +7204,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Sandra Bell</t>
@@ -7234,7 +7234,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Kelly Osborne</t>
@@ -7264,7 +7264,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Stephen Gunther</t>
@@ -7294,7 +7294,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Jeffrey Fox</t>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Franz Humer</t>
@@ -7354,7 +7354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Bryan Murphy</t>
@@ -7384,7 +7384,7 @@
         <v>9.699999999999999</v>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Wilbur Ross</t>
@@ -7414,7 +7414,7 @@
         <v>9.699999999999999</v>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="14" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Anthony Williams</t>
@@ -7444,7 +7444,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Wendy Teramoto</t>
@@ -7474,7 +7474,7 @@
         <v>9.300000000000001</v>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="14" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Thierry Pilenko</t>
@@ -7504,7 +7504,7 @@
         <v>8.699999999999999</v>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="14" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Mohammad Abu-Ghazaleh</t>
@@ -7534,7 +7534,7 @@
         <v>8.699999999999999</v>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
+    <row r="59" ht="14" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
           <t>R. Cox</t>
@@ -7564,7 +7564,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
+    <row r="60" ht="14" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Kathleen Quirk</t>
@@ -7594,7 +7594,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
+    <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Dominic Picone</t>
@@ -7624,7 +7624,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
+    <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Allan D. Schoening</t>
@@ -7654,7 +7654,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
           <t>Daniel Sansone</t>
@@ -7684,7 +7684,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
           <t>David Habachy</t>
@@ -7714,7 +7714,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
           <t>Pam Kaufman</t>
@@ -7744,7 +7744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
+    <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
           <t>Len Blavatnik</t>
@@ -7774,7 +7774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
+    <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Randall Weisenburger</t>
@@ -7804,7 +7804,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
+    <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
           <t>Mark DiPaolo</t>
@@ -7834,7 +7834,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
+    <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>Randle Reece</t>
@@ -7864,7 +7864,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
+    <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
           <t>Tim Cahill</t>
@@ -7894,7 +7894,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
+    <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>Robert Colligan</t>
@@ -7924,7 +7924,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
+    <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
           <t>Brian Corvese</t>
@@ -7954,7 +7954,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
           <t>David Moradi</t>
@@ -7984,7 +7984,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
+    <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
           <t>Tiago Miranda</t>
@@ -8014,7 +8014,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
+    <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
           <t>Charles Leykum</t>
@@ -8044,7 +8044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
           <t>Tony Buffin</t>
@@ -8074,7 +8074,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
+    <row r="77" ht="14" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
           <t>Paul Allen</t>
@@ -8104,7 +8104,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
+    <row r="78" ht="14" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
           <t>David Allen</t>
@@ -8134,7 +8134,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
+    <row r="79" ht="14" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
           <t>Laura Duda</t>
@@ -8164,7 +8164,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
+    <row r="80" ht="14" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
           <t>Oscar Iglesias</t>
@@ -8194,7 +8194,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>Martin Bork</t>
@@ -8224,7 +8224,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
           <t>Haiyan Huang</t>
@@ -8254,7 +8254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
+    <row r="83" ht="14" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>Poh Kiong Tan</t>
@@ -8284,7 +8284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
+    <row r="84" ht="14" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
           <t>Soon Huat Lim</t>
@@ -8314,7 +8314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
+    <row r="85" ht="14" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
           <t>Hock Goh</t>
@@ -8344,7 +8344,7 @@
         <v>4.9</v>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
+    <row r="86" ht="14" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
           <t>Rebecca Grossman-Cohen</t>
@@ -8374,7 +8374,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
+    <row r="87" ht="14" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Michael Denham</t>
@@ -8404,7 +8404,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
+    <row r="88" ht="14" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
           <t>Nicholas Zangler</t>
@@ -8434,7 +8434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
+    <row r="89" ht="14" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Aris Kekedjian</t>
@@ -8464,7 +8464,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
+    <row r="90" ht="14" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
           <t>Phillip Kardis</t>
@@ -8494,7 +8494,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
+    <row r="91" ht="14" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
           <t>Subramaniam Viswanathan</t>
@@ -8524,7 +8524,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
+    <row r="92" ht="14" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
           <t>Anelise Lara</t>
@@ -8554,7 +8554,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
+    <row r="93" ht="14" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
           <t>Josephine Linden</t>
@@ -8584,7 +8584,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
+    <row r="94" ht="14" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
           <t>John McPherson</t>
@@ -8614,7 +8614,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
+    <row r="95" ht="14" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>Richard Massey</t>
@@ -8644,7 +8644,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
+    <row r="96" ht="14" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>John Campbell</t>
@@ -8674,7 +8674,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
+    <row r="97" ht="14" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>Donald Dixon</t>
@@ -8704,7 +8704,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
+    <row r="98" ht="14" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>Sylvia Summers</t>
@@ -8734,7 +8734,7 @@
         <v>2.3</v>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
+    <row r="99" ht="14" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>Alan Ferguson</t>
@@ -8764,7 +8764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
+    <row r="100" ht="14" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
           <t>Alexander Krane</t>
@@ -8794,7 +8794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
+    <row r="101" ht="14" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
           <t>Andrea Pinarel</t>
@@ -8824,7 +8824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
+    <row r="102" ht="14" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
           <t>David Kennedy</t>
@@ -8854,7 +8854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
+    <row r="103" ht="14" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
           <t>Feyyaz Etiz</t>
@@ -8884,7 +8884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
+    <row r="104" ht="14" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
           <t>Gustavo Baquero</t>
@@ -8914,7 +8914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
+    <row r="105" ht="14" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
           <t>Linda Cook</t>
@@ -8944,7 +8944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
+    <row r="106" ht="14" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
           <t>Michael Tuffin</t>
@@ -8974,7 +8974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
+    <row r="107" ht="14" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Nathan Mauzy</t>
@@ -9004,7 +9004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
+    <row r="108" ht="14" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
           <t>Suzanne Wood</t>
@@ -9034,7 +9034,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
+    <row r="109" ht="14" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
           <t>Michael Dougherty</t>
@@ -9064,7 +9064,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
+    <row r="110" ht="14" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
           <t>Dimitris Vastarouchas</t>
@@ -9094,7 +9094,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
+    <row r="111" ht="14" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
           <t>Peter Loscher</t>
@@ -9124,7 +9124,7 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
+    <row r="112" ht="14" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
           <t>Jane O'Keeffe</t>
@@ -9154,7 +9154,7 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
+    <row r="113" ht="14" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
           <t>Arnaud Breuillac</t>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
+    <row r="114" ht="14" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
           <t>Chi-Tung Liu</t>
@@ -9214,7 +9214,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
+    <row r="115" ht="14" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
           <t>Jason Wang</t>
@@ -9244,7 +9244,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
+    <row r="116" ht="14" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
           <t>Raffaele Zagari</t>
@@ -9274,7 +9274,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
+    <row r="117" ht="14" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
           <t>Vuyo Kahla</t>
@@ -9304,7 +9304,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
+    <row r="118" ht="14" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
           <t>Andrew Michelmore</t>
@@ -9334,7 +9334,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
+    <row r="119" ht="14" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
           <t>Massimo Belcredi</t>
@@ -9364,7 +9364,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
+    <row r="120" ht="14" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
           <t>Aviad Kaufman</t>
@@ -9394,7 +9394,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
+    <row r="121" ht="14" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
           <t>Idan Ofer</t>
@@ -9424,7 +9424,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
+    <row r="122" ht="14" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
           <t>Charles Searle</t>
@@ -9454,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
+    <row r="123" ht="14" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
           <t>Chris Siu</t>
@@ -9484,7 +9484,7 @@
         <v>-0</v>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
+    <row r="124" ht="14" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
           <t>Kent Yee</t>
@@ -9514,7 +9514,7 @@
         <v>-1.1</v>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1">
+    <row r="125" ht="14" customHeight="1">
       <c r="A125" s="9" t="inlineStr">
         <is>
           <t>Douglas Rauch</t>
@@ -9544,7 +9544,7 @@
         <v>-1.4</v>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
+    <row r="126" ht="14" customHeight="1">
       <c r="A126" s="9" t="inlineStr">
         <is>
           <t>Miliana Pineda</t>
@@ -9574,7 +9574,7 @@
         <v>-7.2</v>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
+    <row r="127" ht="14" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
         <is>
           <t>Abdul Al-Halabi</t>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
+    <row r="128" ht="14" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
         <is>
           <t>Abdulla Binhabtoor</t>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
+    <row r="129" ht="14" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
           <t>Abdulmajeed Alhaqbani</t>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
+    <row r="130" ht="14" customHeight="1">
       <c r="A130" s="9" t="inlineStr">
         <is>
           <t>Abdulwahab Wazzan</t>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
+    <row r="131" ht="14" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
           <t>Achporn Charuchinda</t>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
+    <row r="132" ht="14" customHeight="1">
       <c r="A132" s="9" t="inlineStr">
         <is>
           <t>Adam Sierakowski</t>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
+    <row r="133" ht="14" customHeight="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
           <t>Adam Sierakowski</t>
@@ -9798,7 +9798,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
+    <row r="134" ht="14" customHeight="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
           <t>Adel Alabdulsalam</t>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
+    <row r="135" ht="14" customHeight="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
           <t>Adrian Casey</t>
@@ -9862,7 +9862,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="18" customHeight="1">
+    <row r="136" ht="14" customHeight="1">
       <c r="A136" s="9" t="inlineStr">
         <is>
           <t>Adrian Ramos</t>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
+    <row r="137" ht="14" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
           <t>Ahmad Al Mujalham</t>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
+    <row r="138" ht="14" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
           <t>Ahmed Altanani</t>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
+    <row r="139" ht="14" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
           <t>Ahmed El Salamouny</t>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
+    <row r="140" ht="14" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
           <t>Ahmed Halawany</t>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
+    <row r="141" ht="14" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
           <t>Al Mawji</t>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1">
+    <row r="142" ht="14" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
           <t>Alain Bacos</t>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
+    <row r="143" ht="14" customHeight="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
           <t>Alan Tang</t>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
+    <row r="144" ht="14" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
           <t>Aleksey Orel</t>
@@ -10150,7 +10150,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
+    <row r="145" ht="14" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
           <t>Alessandro Garrone</t>
@@ -10182,7 +10182,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
+    <row r="146" ht="14" customHeight="1">
       <c r="A146" s="9" t="inlineStr">
         <is>
           <t>Alexander Kempe Cañal de Orozco</t>
@@ -10214,7 +10214,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
+    <row r="147" ht="14" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
           <t>Alexander Kurilov</t>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="18" customHeight="1">
+    <row r="148" ht="14" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
           <t>Alexander Sergeev</t>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
+    <row r="149" ht="14" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
           <t>Alexander Zhuravlev</t>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
+    <row r="150" ht="14" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
           <t>Alfredo Ramos</t>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
+    <row r="151" ht="14" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
           <t>Alistair Cowden</t>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
+    <row r="152" ht="14" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
           <t>Alwaleed al Saud</t>
@@ -10406,7 +10406,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
+    <row r="153" ht="14" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
           <t>Amnat Jiramanimai</t>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="18" customHeight="1">
+    <row r="154" ht="14" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
           <t>Andre Forsterling</t>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
+    <row r="155" ht="14" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
           <t>Andrea Mangion</t>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="18" customHeight="1">
+    <row r="156" ht="14" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
           <t>Andres Finkielsztain</t>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="18" customHeight="1">
+    <row r="157" ht="14" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
           <t>Andrew Barron</t>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
+    <row r="158" ht="14" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
           <t>Andrew Frain</t>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
+    <row r="159" ht="14" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
           <t>André Yché</t>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="18" customHeight="1">
+    <row r="160" ht="14" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
           <t>Andy Torrance</t>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
+    <row r="161" ht="14" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
           <t>Angela Luger</t>
@@ -10694,7 +10694,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="18" customHeight="1">
+    <row r="162" ht="14" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
           <t>Anke Bridge</t>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
+    <row r="163" ht="14" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
           <t>Annabel Roedhammer</t>
@@ -10758,7 +10758,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="18" customHeight="1">
+    <row r="164" ht="14" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
           <t>Anne Stevens</t>
@@ -10790,7 +10790,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
+    <row r="165" ht="14" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
           <t>Antoine Castro</t>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="18" customHeight="1">
+    <row r="166" ht="14" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
           <t>Antonio Serrano</t>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="18" customHeight="1">
+    <row r="167" ht="14" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
           <t>Anu Dhir</t>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="18" customHeight="1">
+    <row r="168" ht="14" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
           <t>Anup Cherian</t>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="18" customHeight="1">
+    <row r="169" ht="14" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
           <t>Arada Jaroon-Ek</t>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
+    <row r="170" ht="14" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
           <t>Arada Vongkusolkit</t>
@@ -10982,7 +10982,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="18" customHeight="1">
+    <row r="171" ht="14" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
           <t>Aseem Gupta</t>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="18" customHeight="1">
+    <row r="172" ht="14" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
           <t>Ashley Paxton</t>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
+    <row r="173" ht="14" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
           <t>Avinash Mansabdar</t>
@@ -11078,7 +11078,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
+    <row r="174" ht="14" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
           <t>Bamdad Bastani</t>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="18" customHeight="1">
+    <row r="175" ht="14" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
           <t>Basim Alothman</t>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="18" customHeight="1">
+    <row r="176" ht="14" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
           <t>Bassim Hokimi</t>
@@ -11174,7 +11174,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="18" customHeight="1">
+    <row r="177" ht="14" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
           <t>Ben Errez</t>
@@ -11206,7 +11206,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="18" customHeight="1">
+    <row r="178" ht="14" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
           <t>Bronwyn Brophy</t>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="18" customHeight="1">
+    <row r="179" ht="14" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
           <t>Bruce Pachkowski</t>
@@ -11270,7 +11270,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="18" customHeight="1">
+    <row r="180" ht="14" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
           <t>Burckhard Bergmann</t>
@@ -11302,7 +11302,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="18" customHeight="1">
+    <row r="181" ht="14" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
           <t>Caesar Maasry</t>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="18" customHeight="1">
+    <row r="182" ht="14" customHeight="1">
       <c r="A182" s="9" t="inlineStr">
         <is>
           <t>Carlos Riquelme</t>
@@ -11366,7 +11366,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="18" customHeight="1">
+    <row r="183" ht="14" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
           <t>Carolyn Ang</t>
@@ -11398,7 +11398,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
+    <row r="184" ht="14" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
         <is>
           <t>Carsten Bachg</t>
@@ -11430,7 +11430,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="18" customHeight="1">
+    <row r="185" ht="14" customHeight="1">
       <c r="A185" s="9" t="inlineStr">
         <is>
           <t>Changxian Beijing</t>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="18" customHeight="1">
+    <row r="186" ht="14" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
           <t>Chantelle Collins</t>
@@ -11494,7 +11494,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="18" customHeight="1">
+    <row r="187" ht="14" customHeight="1">
       <c r="A187" s="9" t="inlineStr">
         <is>
           <t>Charles Xuereb</t>
@@ -11526,7 +11526,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="18" customHeight="1">
+    <row r="188" ht="14" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
         <is>
           <t>Chen Qiuhai</t>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="18" customHeight="1">
+    <row r="189" ht="14" customHeight="1">
       <c r="A189" s="9" t="inlineStr">
         <is>
           <t>Chi Tung Liu</t>
@@ -11590,7 +11590,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="18" customHeight="1">
+    <row r="190" ht="14" customHeight="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
           <t>Chih-Hsien Lo</t>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
+    <row r="191" ht="14" customHeight="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
           <t>Chris McGinnis</t>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="18" customHeight="1">
+    <row r="192" ht="14" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
         <is>
           <t>Christian Windfuhr</t>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="18" customHeight="1">
+    <row r="193" ht="14" customHeight="1">
       <c r="A193" s="9" t="inlineStr">
         <is>
           <t>Christopher Marshall</t>
@@ -11718,7 +11718,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="18" customHeight="1">
+    <row r="194" ht="14" customHeight="1">
       <c r="A194" s="9" t="inlineStr">
         <is>
           <t>Christopher Moreno</t>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="18" customHeight="1">
+    <row r="195" ht="14" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
           <t>Chye Guan</t>
@@ -11782,7 +11782,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="18" customHeight="1">
+    <row r="196" ht="14" customHeight="1">
       <c r="A196" s="9" t="inlineStr">
         <is>
           <t>Clemens Gregor</t>
@@ -11814,7 +11814,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
+    <row r="197" ht="14" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
           <t>Craig Hewitt</t>
@@ -11846,7 +11846,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="18" customHeight="1">
+    <row r="198" ht="14" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
           <t>D. Mark Appleby</t>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="18" customHeight="1">
+    <row r="199" ht="14" customHeight="1">
       <c r="A199" s="9" t="inlineStr">
         <is>
           <t>Dana Codding</t>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="18" customHeight="1">
+    <row r="200" ht="14" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
         <is>
           <t>Daniel Halyk</t>
@@ -11942,7 +11942,7 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="18" customHeight="1">
+    <row r="201" ht="14" customHeight="1">
       <c r="A201" s="9" t="inlineStr">
         <is>
           <t>Daniel Major</t>
@@ -11974,7 +11974,7 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="18" customHeight="1">
+    <row r="202" ht="14" customHeight="1">
       <c r="A202" s="9" t="inlineStr">
         <is>
           <t>Daniel Ninivaggi</t>
@@ -12006,7 +12006,7 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="18" customHeight="1">
+    <row r="203" ht="14" customHeight="1">
       <c r="A203" s="9" t="inlineStr">
         <is>
           <t>Danny Callow</t>
@@ -12038,7 +12038,7 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="18" customHeight="1">
+    <row r="204" ht="14" customHeight="1">
       <c r="A204" s="9" t="inlineStr">
         <is>
           <t>Darwin Green</t>
@@ -12099,7 +12099,7 @@
     <col width="9.5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Network Roster Adds — firms found &amp; now tracked</t>
@@ -12119,7 +12119,7 @@
       <c r="F2" s="3" t="n"/>
     </row>
     <row r="3"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>FUND</t>
@@ -12151,7 +12151,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="14" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Cat Rock Capital Management</t>
@@ -12177,7 +12177,7 @@
         <v>113.6</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="14" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Theleme Partners</t>
@@ -12203,7 +12203,7 @@
         <v>258.1</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Clarkston Capital Partners</t>
@@ -12229,7 +12229,7 @@
         <v>117.9</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Hosking Partners</t>
@@ -12255,7 +12255,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="14" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Tybourne Capital Management</t>
@@ -12281,7 +12281,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="14" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Man Group</t>
@@ -12307,7 +12307,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Mubadala Investment Company</t>

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1.8</v>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>1.2</v>
@@ -2041,98 +2041,98 @@
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>TPG Inc.</t>
+          <t>DFS Furniture plc</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Ingevity Corporation</t>
+          <t>TPG Inc.</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy, Inc.</t>
+          <t>Ingevity Corporation</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -2142,33 +2142,33 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group Corp.</t>
+          <t>Ring Energy, Inc.</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -2178,33 +2178,33 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>Warner Music Group Corp.</t>
         </is>
       </c>
       <c r="C40" s="11" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -2214,33 +2214,33 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Innoviva, Inc.</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -2250,33 +2250,33 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Agenus Inc.</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="C42" s="11" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="E42" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -2286,33 +2286,33 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture plc</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
       <c r="C43" s="11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -2322,91 +2322,91 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Acquisition Corp</t>
+          <t>Agenus Inc.</t>
         </is>
       </c>
       <c r="C44" s="11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Jack Selby</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>ADAG</t>
+          <t>PMTR</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Adagene Inc.</t>
+          <t>Perimeter Acquisition Corp</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Li Li</t>
+          <t>Jack Selby</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>ADAG</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdi</t>
+          <t>Adagene Inc.</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
@@ -2420,33 +2420,33 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Li Li</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>AB SKF (publ)</t>
+          <t>Trident Digital Tech Holdi</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>0</v>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -2466,254 +2466,254 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>AB SKF (publ)</t>
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Sharmila Mulligan</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Stratasys Ltd.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Sharmila Mulligan</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Stratasys Ltd.</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="C51" s="11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="C52" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D52" s="11" t="n">
         <v>3.2</v>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>1.9</v>
       </c>
       <c r="E52" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E53" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silicon Motion Technology </t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E54" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Steve Chen</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -2725,31 +2725,31 @@
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>0086.HK</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>Sun Hung Kai &amp; Co. Limited</t>
         </is>
       </c>
       <c r="C55" s="11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D55" s="11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E55" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>Jacqueline Leung</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -2761,26 +2761,26 @@
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="E56" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -2797,31 +2797,31 @@
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t xml:space="preserve">Silicon Motion Technology </t>
         </is>
       </c>
       <c r="C57" s="11" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D57" s="11" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Steve Chen</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -2833,31 +2833,31 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Houlihan Lokey, Inc.</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="E58" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Tommaso Lillo</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -2869,26 +2869,26 @@
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E59" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -2898,131 +2898,131 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>Houlihan Lokey, Inc.</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="E60" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Tommaso Lillo</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D62" s="11" t="n">
         <v>1.4</v>
       </c>
-      <c r="D62" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E62" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>1</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
@@ -3042,69 +3042,69 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
@@ -3114,33 +3114,33 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E66" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -3150,33 +3150,33 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers Corp.</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
@@ -3186,74 +3186,74 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>SASOF</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Sasol Limited</t>
+          <t>Star Bulk Carriers Corp.</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="E68" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>Vuyo Kahla</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>SASOF</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum Company</t>
+          <t>Sasol Limited</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="E69" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Vuyo Kahla</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
@@ -3265,26 +3265,26 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Century Aluminum Company</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E70" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -3294,19 +3294,19 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings Ltd.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -3330,69 +3330,69 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>WIT</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Wipro Limited</t>
+          <t>Kenon Holdings Ltd.</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E72" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>Rishad Premji</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>ADDYY</t>
+          <t>WIT</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>adidas AG</t>
+          <t>Wipro Limited</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E73" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>Nassef Sawiris</t>
+          <t>Rishad Premji</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
@@ -3402,19 +3402,19 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>UPMMY</t>
+          <t>ADDYY</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>UPM-Kymmene Oyj</t>
+          <t>adidas AG</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>Henrik Ehrnrooth</t>
+          <t>Nassef Sawiris</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
@@ -3438,19 +3438,19 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>UPMMY</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>CK Hutchison Holdings Limi</t>
+          <t>UPM-Kymmene Oyj</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
@@ -3464,29 +3464,29 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>Kwai Wong</t>
+          <t>Henrik Ehrnrooth</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>0086.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Sun Hung Kai &amp; Co. Limited</t>
+          <t>CK Hutchison Holdings Limi</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>Jacqueline Leung</t>
+          <t>Kwai Wong</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="D82" s="11" t="n">
         <v>5.2</v>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="F53" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
@@ -7636,72 +7636,72 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F62" s="11" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -7746,22 +7746,22 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F64" s="11" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -7776,22 +7776,22 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F66" s="11" t="n">
@@ -7816,12 +7816,12 @@
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F67" s="11" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7866,22 +7866,22 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F68" s="11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -7896,22 +7896,22 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -7926,22 +7926,22 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F70" s="11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -7951,27 +7951,27 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F71" s="11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F72" s="11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -8016,22 +8016,22 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F73" s="11" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -8046,22 +8046,22 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F74" s="11" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F75" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -8106,22 +8106,22 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F76" s="11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F77" s="11" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -8166,22 +8166,22 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F78" s="11" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -8196,22 +8196,22 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F79" s="11" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -8226,22 +8226,22 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F80" s="11" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -8251,27 +8251,27 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F81" s="11" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -8286,22 +8286,22 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F82" s="11" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -8316,22 +8316,22 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -8346,22 +8346,22 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F84" s="11" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -8376,22 +8376,22 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -8406,22 +8406,22 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F86" s="11" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Mon</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -8466,22 +8466,22 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F88" s="11" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -8496,22 +8496,22 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F89" s="11" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Phillip Kardis</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -8521,27 +8521,27 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F90" s="11" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Subramaniam Viswanathan</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -8551,27 +8551,27 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F91" s="11" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -8586,22 +8586,22 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F92" s="11" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -8611,27 +8611,27 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -8646,22 +8646,22 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
@@ -8676,22 +8676,22 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>National Bank of Canada (Mon</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -8706,22 +8706,22 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -8736,22 +8736,22 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Stratasys (Printing Services</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -8766,22 +8766,22 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Phillip Kardis</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
@@ -8791,27 +8791,27 @@
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F99" s="11" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Subramaniam Viswanathan</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -8821,27 +8821,27 @@
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
@@ -8856,22 +8856,22 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
@@ -8881,27 +8881,27 @@
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
@@ -8916,22 +8916,22 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F103" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
@@ -8946,22 +8946,22 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F104" s="11" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F105" s="11" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F106" s="11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
@@ -9036,11 +9036,11 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1">
@@ -9166,12 +9166,12 @@
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Jane O'Keeffe</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Bancroft Fund</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>BCV-PA</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F112" s="11" t="n">
@@ -9196,12 +9196,12 @@
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Jane O'Keeffe</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Bancroft Fund</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -9216,11 +9216,11 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>BCV-PA</t>
         </is>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E15" s="11" t="n">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="F16" s="11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -610,7 +610,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sourced from five PitchBook people-searches (1,984 individuals), each filtered to board/advisory roles.</t>
+          <t>Sourced from five PitchBook people-searches (1,983 individuals), each filtered to board/advisory roles.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>13.3</v>
+        <v>17.3</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>4.3</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>1.6</v>
@@ -1273,7 +1273,7 @@
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>RIG</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1283,26 +1283,26 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Under Armour, Inc.</t>
+          <t>Transocean Ltd.</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>38.3</v>
+        <v>32.4</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Margareth Ovrum</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -1312,14 +1312,14 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>RIG</t>
+          <t>HGV</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1329,26 +1329,26 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Transocean Ltd.</t>
+          <t>Hilton Grand Vacations Inc</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>32.7</v>
+        <v>23.4</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Margareth Ovrum</t>
+          <t>Leonard Potter</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>HGV</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1375,26 +1375,26 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations Inc</t>
+          <t>Charter Communications, In</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>22.6</v>
+        <v>20.6</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Leonard Potter</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -1404,14 +1404,14 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1421,14 +1421,14 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications, In</t>
+          <t>QXO, Inc.</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>19.7</v>
+        <v>17.5</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>1</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1450,14 +1450,14 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1467,26 +1467,26 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers, Inc.</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>19.7</v>
+        <v>17.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1513,26 +1513,26 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>Under Armour, Inc.</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>16.6</v>
+        <v>14.9</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1588,14 +1588,14 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1605,14 +1605,14 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>QXO, Inc.</t>
+          <t>Toll Brothers, Inc.</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1697,26 +1697,26 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy, Inc.</t>
+          <t>Coya Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>1999</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1743,26 +1743,26 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee Company</t>
+          <t>SandRidge Energy, Inc.</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>1999</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics, Inc.</t>
+          <t>Westrock Coffee Company</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2019,14 +2019,14 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Acquisition Corp</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1</v>
@@ -2038,24 +2038,24 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Jack Selby</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>PMTR</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2065,14 +2065,14 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>AB SKF (publ)</t>
+          <t>Perimeter Acquisition Corp</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -2084,17 +2084,17 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Jack Selby</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>6.1</v>
@@ -2147,7 +2147,7 @@
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -2157,14 +2157,14 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>AB SKF (publ)</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>1</v>
@@ -2176,17 +2176,17 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum Company</t>
+          <t>Oklo Inc.</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>1996</t>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Samuel Altman</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>1.7</v>
@@ -2377,7 +2377,7 @@
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1</v>
@@ -2406,24 +2406,24 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2433,14 +2433,14 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
@@ -2452,17 +2452,17 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -2709,36 +2709,36 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Oklo Inc.</t>
+          <t>Century Aluminum Company</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>-2.8</v>
+        <v>-3.6</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>1996</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Samuel Altman</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>35.7</v>
+        <v>34.8</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>1.9</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>1.4</v>
@@ -2837,7 +2837,7 @@
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2847,26 +2847,26 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.9</v>
+        <v>9</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2893,26 +2893,26 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>1</v>
@@ -2958,24 +2958,24 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2985,14 +2985,14 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings, Inc.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>FRP Holdings, Inc.</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
@@ -3050,17 +3050,17 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -3307,26 +3307,26 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global, Inc.</t>
+          <t>Allogene Therapeutics, Inc</t>
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>LanzaTech Global, Inc.</t>
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1</v>
@@ -3372,17 +3372,17 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>1.2</v>
@@ -3435,7 +3435,7 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -3445,36 +3445,36 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics, Inc</t>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>ADAG</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3629,14 +3629,14 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Adagene Inc.</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -3648,24 +3648,24 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Li Li</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>ADAG</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdi</t>
+          <t>Adagene Inc.</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
@@ -3687,31 +3687,31 @@
       <c r="F63" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Li Li</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3721,43 +3721,43 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Trident Digital Tech Holdi</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -3767,14 +3767,14 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
@@ -3786,24 +3786,24 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>1</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3842,14 +3842,14 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3859,14 +3859,14 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
@@ -3878,24 +3878,24 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3905,26 +3905,26 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="E69" s="11" t="n">
         <v>0.8</v>
@@ -3987,7 +3987,7 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -3997,26 +3997,26 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4043,26 +4043,26 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -4089,43 +4089,43 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>2003</t>
+        <v>1</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -4135,43 +4135,43 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E73" s="11" t="n">
         <v>1.4</v>
       </c>
-      <c r="E73" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="F73" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -4181,43 +4181,43 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>Sprouts Farmers Market, In</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -4256,14 +4256,14 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -4273,26 +4273,26 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>2022</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, In</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>-0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>1</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -4365,14 +4365,14 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>5.2</v>
+        <v>0.1</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -4384,17 +4384,17 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>-6.2</v>
+        <v>-5.2</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>1.3</v>
@@ -4541,66 +4541,66 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Keith Rabois</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Capital</t>
+          <t>tracked principal</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Chairman &amp; Board Membe</t>
+          <t>Board Member</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Keith Rabois</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>tracked principal</t>
+          <t>Sequoia Capital</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>DarioHealth</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>13.3</v>
+        <v>17</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Board Member</t>
+          <t>Chairman &amp; Board Membe</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>1</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>1.6</v>
@@ -5625,12 +5625,12 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Margareth Ovrum</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Transocean</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -5645,22 +5645,22 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>RIG</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>38.3</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Margareth Ovrum</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Transocean</t>
+          <t>Lindblad Expeditions Holding</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -5675,52 +5675,52 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>RIG</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holding</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>28.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Leonard Potter</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5735,52 +5735,52 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>HGV</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>27.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Leonard Potter</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -5795,22 +5795,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>HGV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -5855,22 +5855,22 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -5885,22 +5885,22 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5915,22 +5915,22 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -5945,22 +5945,22 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -5975,22 +5975,22 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -6005,22 +6005,22 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -6035,22 +6035,22 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -6065,22 +6065,22 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -6095,22 +6095,22 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -6165,7 +6165,7 @@
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -6225,7 +6225,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -6375,7 +6375,7 @@
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -6405,7 +6405,7 @@
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -6435,12 +6435,12 @@
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -6455,22 +6455,22 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -6485,22 +6485,22 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>David Wright</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Rezolve Ai</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -6510,27 +6510,27 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>RZLVW</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>David Wright</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Rezolve Ai</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -6540,27 +6540,27 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>RZLVW</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>Richard Russell</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>LM Funding America</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>LMFA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Servi</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -6605,22 +6605,22 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Richard Russell</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>LM Funding America</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -6635,22 +6635,22 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>LMFA</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -6665,22 +6665,22 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -6695,17 +6695,17 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -6735,12 +6735,12 @@
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>Joseph Flaim</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Iamgold</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -6750,27 +6750,27 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Joseph Flaim</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Iamgold</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -6780,27 +6780,27 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Frates</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Jonathan Frates</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -6885,12 +6885,12 @@
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6905,11 +6905,11 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
@@ -6939,18 +6939,18 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Sandra Bell</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Dye &amp; Durham</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -6960,27 +6960,27 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>DYNDF</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Kelly Osborne</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Kinross Gold</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>KGCRF</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Sandra Bell</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Dye &amp; Durham</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -7025,22 +7025,22 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DYNDF</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -7050,16 +7050,16 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
@@ -7089,18 +7089,18 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Kelly Osborne</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>Kinross Gold</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -7115,22 +7115,22 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>KGCRF</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -7145,22 +7145,22 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>Uniti Group (Financial Servi</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -7175,22 +7175,22 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>The Greenbrier Companies</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -7235,22 +7235,22 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -7265,11 +7265,11 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
@@ -7299,78 +7299,78 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -7385,22 +7385,22 @@
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -7415,22 +7415,22 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
@@ -7455,12 +7455,12 @@
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -7505,22 +7505,22 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
@@ -7545,12 +7545,12 @@
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
@@ -7575,12 +7575,12 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -7590,16 +7590,16 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
@@ -7635,12 +7635,12 @@
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
@@ -7665,12 +7665,12 @@
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7685,22 +7685,22 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -7715,22 +7715,22 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -7775,22 +7775,22 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -7805,22 +7805,22 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
@@ -7845,12 +7845,12 @@
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -7860,27 +7860,27 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -7895,22 +7895,22 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
@@ -7935,12 +7935,12 @@
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -7955,22 +7955,22 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
@@ -7995,7 +7995,7 @@
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -8025,12 +8025,12 @@
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
@@ -8055,12 +8055,12 @@
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -8075,22 +8075,22 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Mon</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -8105,22 +8105,22 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -8130,27 +8130,27 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>National Bank of Canada (Mon</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -8165,22 +8165,22 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -8195,22 +8195,22 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Phillip Kardis</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -8220,27 +8220,27 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Subramaniam Viswanathan</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Stratasys (Printing Services</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -8250,27 +8250,27 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Phillip Kardis</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -8280,27 +8280,27 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Subramaniam Viswanathan</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -8310,16 +8310,16 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
@@ -8355,12 +8355,12 @@
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -8375,22 +8375,22 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -8405,22 +8405,22 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
@@ -8465,22 +8465,22 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -8495,17 +8495,17 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -8535,7 +8535,7 @@
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8595,7 +8595,7 @@
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -8625,7 +8625,7 @@
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -8655,7 +8655,7 @@
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -8685,7 +8685,7 @@
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
@@ -8715,12 +8715,12 @@
     <row r="108" ht="14" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
@@ -8735,22 +8735,22 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" ht="14" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
@@ -8765,22 +8765,22 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -8795,22 +8795,22 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -8820,27 +8820,27 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
@@ -8865,12 +8865,12 @@
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
@@ -8895,12 +8895,12 @@
     <row r="114" ht="14" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
@@ -8925,12 +8925,12 @@
     <row r="115" ht="14" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
@@ -9195,12 +9195,12 @@
     <row r="124" ht="14" customHeight="1">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Kent Yee</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>DXP Enterprises</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -9215,22 +9215,22 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="F124" s="12" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="125" ht="14" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>Kent Yee</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>DXP Enterprises</t>
+          <t>Century Aluminum</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -9245,11 +9245,11 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="F125" s="12" t="n">
-        <v>-1.1</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="126" ht="14" customHeight="1">
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="F126" s="12" t="n">
-        <v>-6.2</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'README'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Board Signal — In Universe'!$A$4:$J$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Board Signal — In Universe'!$A$4:$J$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Board Signal — In Universe'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Investor Board Seats'!$A$4:$G$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Investor Board Seats'!$1:$4</definedName>
@@ -624,7 +624,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>75 land on companies inside our tradeable universe and carry a live smart-money score.</t>
+          <t>76 land on companies inside our tradeable universe and carry a live smart-money score.</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1014,7 +1014,7 @@
         <v>17.3</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>1</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>1</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>1</v>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>1</v>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1421,26 +1421,26 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>QXO, Inc.</t>
+          <t>Monro, Inc.</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>2012</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -1450,14 +1450,14 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1467,26 +1467,26 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Monro, Inc.</t>
+          <t>QXO, Inc.</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>17.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>2012</t>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>1</v>
@@ -1704,7 +1704,7 @@
         <v>12.7</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>1</v>
@@ -1779,7 +1779,7 @@
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1789,26 +1789,26 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee Company</t>
+          <t xml:space="preserve">The Greenbrier Companies, </t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1818,14 +1818,14 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1835,26 +1835,26 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Greenbrier Companies, </t>
+          <t>Westrock Coffee Company</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1.9</v>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>1</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>1</v>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="D37" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E37" s="11" t="n">
         <v>0.2</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0.1</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>UPMMY</t>
+          <t>HTZ 8 07-15-29</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -2523,13 +2523,13 @@
           <t>B</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>UPM-Kymmene Oyj</t>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>0</v>
@@ -2537,31 +2537,31 @@
       <c r="F38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>1988</t>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Henrik Ehrnrooth</t>
+          <t>Vincent Intrieri</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
+          <t>Billionaire/Oligarch Veh</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>0001.HK</t>
+          <t>UPMMY</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>CK Hutchison Holdings Limi</t>
+          <t>UPM-Kymmene Oyj</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
@@ -2583,31 +2583,31 @@
       <c r="F39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>1988</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>Kwai Wong</t>
+          <t>Henrik Ehrnrooth</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0001.HK</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Tencent Holdings Limited</t>
+          <t>CK Hutchison Holdings Limi</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
@@ -2636,24 +2636,24 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Kwai Wong</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>360ONE.NS</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>360 One Wam Limited</t>
+          <t>Tencent Holdings Limited</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
@@ -2682,24 +2682,24 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>Akhil Gupta</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network,Gulf/Roy</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>360ONE.NS</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -2709,89 +2709,89 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum Company</t>
+          <t>360 One Wam Limited</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>1996</t>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Akhil Gupta</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network,Gulf/Roy</t>
         </is>
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Republic Services, Inc.</t>
+          <t>Century Aluminum Company</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
-        <v>34.8</v>
+        <v>-3.6</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>1996</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -2801,43 +2801,43 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holdi</t>
+          <t>Republic Services, Inc.</t>
         </is>
       </c>
       <c r="D44" s="11" t="n">
-        <v>29.3</v>
+        <v>34.8</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>2022</t>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2847,26 +2847,26 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>Lindblad Expeditions Holdi</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>19.9</v>
+        <v>29.4</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2893,26 +2893,26 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>1</v>
@@ -2958,24 +2958,24 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>6.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -3077,26 +3077,26 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>VEON Ltd.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
+        <v>1</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis,Duncan Perry</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -3123,14 +3123,14 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth Corp.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>1</v>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -3169,26 +3169,26 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>VEON Ltd.</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
+          <t>Brandon Lewis,Duncan Perry</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3198,14 +3198,14 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA, Inc.</t>
+          <t>DarioHealth Corp.</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Everest Group, Ltd.</t>
+          <t>Beazer Homes USA, Inc.</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>13.5</v>
+        <v>16.1</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="D55" s="11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>1</v>
@@ -3343,7 +3343,7 @@
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global, Inc.</t>
+          <t>Everest Group, Ltd.</t>
         </is>
       </c>
       <c r="D56" s="11" t="n">
-        <v>10.7</v>
+        <v>13</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3382,14 +3382,14 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>UPWK</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -3397,16 +3397,16 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Upwork Inc.</t>
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="E57" s="11" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>1</v>
@@ -3418,24 +3418,24 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Glenn Kelman</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Sequoia Network</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>UPWK</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Upwork Inc.</t>
+          <t>LanzaTech Global, Inc.</t>
         </is>
       </c>
       <c r="D58" s="11" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="F58" s="12" t="n">
         <v>1</v>
@@ -3464,24 +3464,24 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Glenn Kelman</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -3489,16 +3489,16 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>Ingevity Corporation</t>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D59" s="11" t="n">
-        <v>7.3</v>
+        <v>10.4</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>1</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3518,9 +3518,9 @@
           <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
+      <c r="J59" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
@@ -3573,7 +3573,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Ingevity Corporation</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3629,14 +3629,14 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>MP Materials Corp.</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3658,14 +3658,14 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>ADAG</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -3675,14 +3675,14 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Adagene Inc.</t>
+          <t>MP Materials Corp.</t>
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -3694,24 +3694,24 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>Li Li</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>ADAG</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -3721,43 +3721,43 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdi</t>
+          <t>Adagene Inc.</t>
         </is>
       </c>
       <c r="D64" s="11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Li Li</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -3767,43 +3767,43 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>Trident Digital Tech Holdi</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>1</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3842,14 +3842,14 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3859,14 +3859,14 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3888,14 +3888,14 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3905,14 +3905,14 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>3.2</v>
+        <v>0.1</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
@@ -3924,24 +3924,24 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -3997,26 +3997,26 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4043,26 +4043,26 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -4089,26 +4089,26 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -4135,43 +4135,43 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>Sprouts Farmers Market, In</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>2003</t>
+        <v>1</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -4181,43 +4181,43 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -4227,26 +4227,26 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, In</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E75" s="11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>1.7</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>2022</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -4256,14 +4256,14 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -4273,43 +4273,43 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>1</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -4365,14 +4365,14 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4394,14 +4394,14 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -4411,14 +4411,14 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>-5.2</v>
+        <v>0.2</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>1</v>
@@ -4430,22 +4430,68 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
+          <t>Massimo Belcredi</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Billionaire/Oligarch Veh</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>BROS</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Dutch Bros Inc.</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
           <t>Miliana Pineda</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr">
+      <c r="J80" s="10" t="inlineStr">
         <is>
           <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J79"/>
+  <autoFilter ref="A4:J80"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -4563,7 +4609,7 @@
         <v>17.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
@@ -4626,10 +4672,10 @@
         </is>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -4659,10 +4705,10 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -4692,10 +4738,10 @@
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -5561,7 +5607,7 @@
     <col width="30.5" customWidth="1" min="2" max="2"/>
     <col width="22.5" customWidth="1" min="3" max="3"/>
     <col width="24.5" customWidth="1" min="4" max="4"/>
-    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="16.5" customWidth="1" min="5" max="5"/>
     <col width="11.5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5649,7 +5695,7 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -5679,7 +5725,7 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -5709,7 +5755,7 @@
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -5739,18 +5785,18 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -5765,7 +5811,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
@@ -5775,12 +5821,12 @@
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -5795,22 +5841,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22.4</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -5825,11 +5871,11 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>20.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -5859,7 +5905,7 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -5895,12 +5941,12 @@
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5915,22 +5961,22 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -5945,22 +5991,22 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -5975,22 +6021,22 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -6005,22 +6051,22 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -6035,22 +6081,22 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -6065,22 +6111,22 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>17.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -6095,17 +6141,17 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>17.3</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6129,13 +6175,13 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -6159,13 +6205,13 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -6189,13 +6235,13 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -6219,18 +6265,18 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -6245,22 +6291,22 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -6275,22 +6321,22 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -6305,22 +6351,22 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>17</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -6335,22 +6381,22 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -6365,22 +6411,22 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -6395,22 +6441,22 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -6425,11 +6471,11 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -6489,7 +6535,7 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -6519,7 +6565,7 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -6639,18 +6685,18 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -6665,11 +6711,11 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
@@ -6699,7 +6745,7 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
@@ -6729,7 +6775,7 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -6759,18 +6805,18 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -6785,22 +6831,22 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6815,22 +6861,22 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -6845,11 +6891,11 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
@@ -6945,12 +6991,12 @@
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>The Greenbrier Companies</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -6965,11 +7011,11 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -7005,12 +7051,12 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Sandra Bell</t>
+          <t>Kelly Osborne</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Dye &amp; Durham</t>
+          <t>Kinross Gold</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -7020,27 +7066,27 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>DYNDF</t>
+          <t>KGCRF</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -7050,27 +7096,27 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Sandra Bell</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Dye &amp; Durham</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -7080,27 +7126,27 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>DYNDF</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Kelly Osborne</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Kinross Gold</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -7110,27 +7156,27 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>KGCRF</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Uniti Group (Financial Servi</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -7145,22 +7191,22 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Servi</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -7175,22 +7221,22 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -7205,22 +7251,22 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -7235,22 +7281,22 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -7265,27 +7311,27 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Mohammad Abu-Ghazaleh</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Fresh Del Monte Produce</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -7295,27 +7341,27 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Mohammad Abu-Ghazaleh</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>Fresh Del Monte Produce</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -7325,22 +7371,22 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -7355,22 +7401,22 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Robert Colligan</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Dynex Capital</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -7380,27 +7426,27 @@
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>Len Blavatnik</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -7415,22 +7461,22 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Len Blavatnik</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -7445,11 +7491,11 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
@@ -7479,18 +7525,18 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -7505,22 +7551,22 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7535,7 +7581,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
@@ -7545,12 +7591,12 @@
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Robert Colligan</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Dynex Capital</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -7560,12 +7606,12 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
@@ -7575,12 +7621,12 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -7595,7 +7641,7 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
@@ -7635,12 +7681,12 @@
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7655,22 +7701,22 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7685,22 +7731,22 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -7715,7 +7761,7 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
@@ -7749,7 +7795,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
@@ -7815,12 +7861,12 @@
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Paul Allen</t>
+          <t>Martin Bork</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Airship AI Holdings</t>
+          <t>Navigator Holdings</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -7835,7 +7881,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>AISP</t>
+          <t>NVGS</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
@@ -7869,18 +7915,18 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Martin Bork</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Navigator Holdings</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -7895,22 +7941,22 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>NVGS</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -7925,7 +7971,7 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
@@ -7935,12 +7981,12 @@
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Paul Allen</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>Airship AI Holdings</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -7955,22 +8001,22 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>AISP</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -7985,7 +8031,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
@@ -7995,7 +8041,7 @@
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -8025,7 +8071,7 @@
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -8055,12 +8101,12 @@
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -8075,22 +8121,22 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>National Bank of Canada (Mon</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -8105,11 +8151,11 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
@@ -8139,18 +8185,18 @@
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Mon</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -8165,22 +8211,22 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -8195,7 +8241,7 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
@@ -8205,12 +8251,12 @@
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -8225,7 +8271,7 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
@@ -8349,7 +8395,7 @@
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
@@ -8379,7 +8425,7 @@
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
@@ -8469,7 +8515,7 @@
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
@@ -8775,12 +8821,12 @@
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -8795,22 +8841,22 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -8825,22 +8871,22 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -8850,27 +8896,27 @@
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -8880,27 +8926,27 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -8915,7 +8961,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
@@ -8925,12 +8971,12 @@
     <row r="115" ht="14" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Jane O'Keeffe</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>Bancroft Fund</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
@@ -8945,7 +8991,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>BCV-PA</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
@@ -8955,12 +9001,12 @@
     <row r="116" ht="14" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Jane O'Keeffe</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>Bancroft Fund</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -8975,11 +9021,11 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>BCV-PA</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1">
@@ -9009,7 +9055,7 @@
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="118" ht="14" customHeight="1">
@@ -9039,7 +9085,7 @@
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -9075,12 +9121,12 @@
     <row r="120" ht="14" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -9095,17 +9141,17 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="121" ht="14" customHeight="1">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Idan Ofer</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -9129,18 +9175,18 @@
         </is>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="122" ht="14" customHeight="1">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>Idan Ofer</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -9155,7 +9201,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
@@ -9165,12 +9211,12 @@
     <row r="123" ht="14" customHeight="1">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>Charles Searle</t>
+          <t>Vincent Intrieri</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Tencent Holdings</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
@@ -9185,22 +9231,22 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>HTZ 8 07-15-29</t>
         </is>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>Kent Yee</t>
+          <t>Charles Searle</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>DXP Enterprises</t>
+          <t>Tencent Holdings</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
@@ -9215,22 +9261,22 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="F124" s="12" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" ht="14" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>Andrew Michelmore</t>
+          <t>Kent Yee</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>Century Aluminum</t>
+          <t>DXP Enterprises</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
@@ -9245,22 +9291,22 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="F125" s="12" t="n">
-        <v>-3.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="126" ht="14" customHeight="1">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Miliana Pineda</t>
+          <t>Andrew Michelmore</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>Dutch Bros</t>
+          <t>Century Aluminum</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
@@ -9275,59 +9321,57 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="F126" s="12" t="n">
-        <v>-5.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Abdul Al-Halabi</t>
+          <t>Miliana Pineda</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>Embassy Capital</t>
+          <t>Dutch Bros</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Billionaire/Oligarch V</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>BROS</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>-5.2</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Abdulla Binhabtoor</t>
+          <t>Abdul Al-Halabi</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>Shamal Holding</t>
+          <t>Embassy Capital</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -9349,17 +9393,17 @@
     <row r="129" ht="14" customHeight="1">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Abdulmajeed Alhaqbani</t>
+          <t>Abdulla Binhabtoor</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>Shamal Holding</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
@@ -9381,17 +9425,17 @@
     <row r="130" ht="14" customHeight="1">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Abdulwahab Wazzan</t>
+          <t>Abdulmajeed Alhaqbani</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>National International Holdi</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -9413,12 +9457,12 @@
     <row r="131" ht="14" customHeight="1">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Achporn Charuchinda</t>
+          <t>Abdulwahab Wazzan</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>Bangchak Corporation</t>
+          <t>National International Holdi</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
@@ -9445,12 +9489,12 @@
     <row r="132" ht="14" customHeight="1">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Adam Sierakowski</t>
+          <t>Achporn Charuchinda</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>Kinetiko Energy</t>
+          <t>Bangchak Corporation</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
@@ -9460,7 +9504,7 @@
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -9482,7 +9526,7 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>Raptor Resources (Other Meta</t>
+          <t>Kinetiko Energy</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
@@ -9509,22 +9553,22 @@
     <row r="134" ht="14" customHeight="1">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Adel Alabdulsalam</t>
+          <t>Adam Sierakowski</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>Raptor Resources (Other Meta</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -9541,22 +9585,22 @@
     <row r="135" ht="14" customHeight="1">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Adrian Casey</t>
+          <t>Adel Alabdulsalam</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Steel (Industrial Sup</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
@@ -9573,12 +9617,12 @@
     <row r="136" ht="14" customHeight="1">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>Adrian Ramos</t>
+          <t>Adrian Casey</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>Atlas CON Mining</t>
+          <t>Vulcan Steel (Industrial Sup</t>
         </is>
       </c>
       <c r="C136" s="10" t="inlineStr">
@@ -9605,12 +9649,12 @@
     <row r="137" ht="14" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Ahmad Al Mujalham</t>
+          <t>Adrian Ramos</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Shamal Az-Zour Al-Oula</t>
+          <t>Atlas CON Mining</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
@@ -9620,7 +9664,7 @@
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -9637,17 +9681,17 @@
     <row r="138" ht="14" customHeight="1">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Altanani</t>
+          <t>Ahmad Al Mujalham</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Shamal Az-Zour Al-Oula</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
@@ -9669,17 +9713,17 @@
     <row r="139" ht="14" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Ahmed El Salamouny</t>
+          <t>Ahmed Altanani</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>National International Holdi</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
@@ -9701,17 +9745,17 @@
     <row r="140" ht="14" customHeight="1">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Halawany</t>
+          <t>Ahmed El Salamouny</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>SIGMA Capital Holding</t>
+          <t>National International Holdi</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
@@ -9733,17 +9777,17 @@
     <row r="141" ht="14" customHeight="1">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Al Mawji</t>
+          <t>Ahmed Halawany</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>SIGMA Capital Holding</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
@@ -9765,7 +9809,7 @@
     <row r="142" ht="14" customHeight="1">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>Alain Bacos</t>
+          <t>Al Mawji</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -9797,22 +9841,22 @@
     <row r="143" ht="14" customHeight="1">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Alan Tang</t>
+          <t>Alain Bacos</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>Far East Orchard</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -9829,12 +9873,12 @@
     <row r="144" ht="14" customHeight="1">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>Aleksey Orel</t>
+          <t>Alan Tang</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>NOVATEK (Russia</t>
+          <t>Far East Orchard</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
@@ -9861,12 +9905,12 @@
     <row r="145" ht="14" customHeight="1">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Alessandro Garrone</t>
+          <t>Aleksey Orel</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>De Nora</t>
+          <t>NOVATEK (Russia</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
@@ -9893,22 +9937,22 @@
     <row r="146" ht="14" customHeight="1">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>Alexander Kempe Cañal de Orozco</t>
+          <t>Alessandro Garrone</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>37celsius Capital Partners</t>
+          <t>De Nora</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -9925,22 +9969,22 @@
     <row r="147" ht="14" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Alexander Kurilov</t>
+          <t>Alexander Kempe Cañal de Orozco</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>Pharmacy Chain 36.6</t>
+          <t>37celsius Capital Partners</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -9957,12 +10001,12 @@
     <row r="148" ht="14" customHeight="1">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Alexander Sergeev</t>
+          <t>Alexander Kurilov</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>En+ Group</t>
+          <t>Pharmacy Chain 36.6</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
@@ -9989,22 +10033,22 @@
     <row r="149" ht="14" customHeight="1">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>Alexander Zhuravlev</t>
+          <t>Alexander Sergeev</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>En+ Group</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -10021,22 +10065,22 @@
     <row r="150" ht="14" customHeight="1">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>Alfredo Ramos</t>
+          <t>Alexander Zhuravlev</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>Atlas CON Mining</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
@@ -10053,12 +10097,12 @@
     <row r="151" ht="14" customHeight="1">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>Alistair Cowden</t>
+          <t>Alfredo Ramos</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>Firefinch</t>
+          <t>Atlas CON Mining</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
@@ -10085,22 +10129,22 @@
     <row r="152" ht="14" customHeight="1">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>Alwaleed al Saud</t>
+          <t>Alistair Cowden</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>Kingdom Holding Company</t>
+          <t>Firefinch</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
@@ -10117,17 +10161,17 @@
     <row r="153" ht="14" customHeight="1">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>Amnat Jiramanimai</t>
+          <t>Alwaleed al Saud</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>The Crown Property Bureau</t>
+          <t>Kingdom Holding Company</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
@@ -10149,17 +10193,17 @@
     <row r="154" ht="14" customHeight="1">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>Andre Forsterling</t>
+          <t>Amnat Jiramanimai</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>The Crown Property Bureau</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
@@ -10181,22 +10225,22 @@
     <row r="155" ht="14" customHeight="1">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>Andrea Mangion</t>
+          <t>Andre Forsterling</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>Trident Estates</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -10213,12 +10257,12 @@
     <row r="156" ht="14" customHeight="1">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>Andres Finkielsztain</t>
+          <t>Andrea Mangion</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>Menē</t>
+          <t>Trident Estates</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
@@ -10245,12 +10289,12 @@
     <row r="157" ht="14" customHeight="1">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>Andrew Barron</t>
+          <t>Andres Finkielsztain</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>Natcore Technology</t>
+          <t>Menē</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
@@ -10260,7 +10304,7 @@
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -10277,12 +10321,12 @@
     <row r="158" ht="14" customHeight="1">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>Andrew Frain</t>
+          <t>Andrew Barron</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>Shamal Az-Zour Al-Oula</t>
+          <t>Natcore Technology</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
@@ -10309,17 +10353,17 @@
     <row r="159" ht="14" customHeight="1">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>André Yché</t>
+          <t>Andrew Frain</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>CDC Habitat</t>
+          <t>Shamal Az-Zour Al-Oula</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
@@ -10341,22 +10385,22 @@
     <row r="160" ht="14" customHeight="1">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>Andy Torrance</t>
+          <t>André Yché</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>Angling Direct</t>
+          <t>CDC Habitat</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -10373,12 +10417,12 @@
     <row r="161" ht="14" customHeight="1">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>Angela Luger</t>
+          <t>Andy Torrance</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>JD Sports Fashion</t>
+          <t>Angling Direct</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
@@ -10405,22 +10449,22 @@
     <row r="162" ht="14" customHeight="1">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>Anke Bridge</t>
+          <t>Angela Luger</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>LGT Group</t>
+          <t>JD Sports Fashion</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Family Office (Multi</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -10437,22 +10481,22 @@
     <row r="163" ht="14" customHeight="1">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>Annabel Roedhammer</t>
+          <t>Anke Bridge</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>LGT Group</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Family Office (Multi</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -10469,12 +10513,12 @@
     <row r="164" ht="14" customHeight="1">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>Anne Stevens</t>
+          <t>Annabel Roedhammer</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aston Martin Lagonda Global </t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
@@ -10501,12 +10545,12 @@
     <row r="165" ht="14" customHeight="1">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>Antoine Castro</t>
+          <t>Anne Stevens</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>Paref</t>
+          <t xml:space="preserve">Aston Martin Lagonda Global </t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
@@ -10533,12 +10577,12 @@
     <row r="166" ht="14" customHeight="1">
       <c r="A166" s="10" t="inlineStr">
         <is>
-          <t>Antonio Serrano</t>
+          <t>Antoine Castro</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>Grupo Dia (Department Stores</t>
+          <t>Paref</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
@@ -10565,12 +10609,12 @@
     <row r="167" ht="14" customHeight="1">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>Anu Dhir</t>
+          <t>Antonio Serrano</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>Capital</t>
+          <t>Grupo Dia (Department Stores</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
@@ -10597,22 +10641,22 @@
     <row r="168" ht="14" customHeight="1">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>Anup Cherian</t>
+          <t>Anu Dhir</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Capital</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -10629,17 +10673,17 @@
     <row r="169" ht="14" customHeight="1">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>Arada Jaroon-Ek</t>
+          <t>Anup Cherian</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>Origin Property</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
@@ -10661,12 +10705,12 @@
     <row r="170" ht="14" customHeight="1">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>Arada Vongkusolkit</t>
+          <t>Arada Jaroon-Ek</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>Erawan Group</t>
+          <t>Origin Property</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
@@ -10693,17 +10737,17 @@
     <row r="171" ht="14" customHeight="1">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>Aseem Gupta</t>
+          <t>Arada Vongkusolkit</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Erawan Group</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
@@ -10725,22 +10769,22 @@
     <row r="172" ht="14" customHeight="1">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>Ashley Paxton</t>
+          <t>Aseem Gupta</t>
         </is>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Ikigai Ventures Limited</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
@@ -10757,22 +10801,22 @@
     <row r="173" ht="14" customHeight="1">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>Avinash Mansabdar</t>
+          <t>Ashley Paxton</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>The Private Office of Sheikh</t>
+          <t>Ikigai Ventures Limited</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Family Office (Singl</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -10789,22 +10833,22 @@
     <row r="174" ht="14" customHeight="1">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>Bamdad Bastani</t>
+          <t>Avinash Mansabdar</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>IQE</t>
+          <t>The Private Office of Sheikh</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Family Office (Singl</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
@@ -10821,12 +10865,12 @@
     <row r="175" ht="14" customHeight="1">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>Basim Alothman</t>
+          <t>Bamdad Bastani</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>Coast Investment</t>
+          <t>IQE</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
@@ -10836,7 +10880,7 @@
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
@@ -10853,17 +10897,17 @@
     <row r="176" ht="14" customHeight="1">
       <c r="A176" s="10" t="inlineStr">
         <is>
-          <t>Bassim Hokimi</t>
+          <t>Basim Alothman</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Atlamed</t>
+          <t>Coast Investment</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
@@ -10885,17 +10929,17 @@
     <row r="177" ht="14" customHeight="1">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>Ben Errez</t>
+          <t>Bassim Hokimi</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>RYVYL</t>
+          <t>Atlamed</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
@@ -10917,12 +10961,12 @@
     <row r="178" ht="14" customHeight="1">
       <c r="A178" s="10" t="inlineStr">
         <is>
-          <t>Bronwyn Brophy</t>
+          <t>Ben Errez</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Vitrolife</t>
+          <t>RYVYL</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
@@ -10932,7 +10976,7 @@
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
@@ -10949,12 +10993,12 @@
     <row r="179" ht="14" customHeight="1">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>Bruce Pachkowski</t>
+          <t>Bronwyn Brophy</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>Total Energy Services</t>
+          <t>Vitrolife</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
@@ -10981,12 +11025,12 @@
     <row r="180" ht="14" customHeight="1">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>Burckhard Bergmann</t>
+          <t>Bruce Pachkowski</t>
         </is>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>NOVATEK (Russia</t>
+          <t>Total Energy Services</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
@@ -11013,22 +11057,22 @@
     <row r="181" ht="14" customHeight="1">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>Caesar Maasry</t>
+          <t>Burckhard Bergmann</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>NOVATEK (Russia</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
@@ -11045,17 +11089,17 @@
     <row r="182" ht="14" customHeight="1">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t>Carlos Riquelme</t>
+          <t>Caesar Maasry</t>
         </is>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Prince of Wales Country Club</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
@@ -11077,17 +11121,17 @@
     <row r="183" ht="14" customHeight="1">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>Carolyn Ang</t>
+          <t>Carlos Riquelme</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>Lunate</t>
+          <t>Prince of Wales Country Club</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
@@ -11109,22 +11153,22 @@
     <row r="184" ht="14" customHeight="1">
       <c r="A184" s="10" t="inlineStr">
         <is>
-          <t>Carsten Bachg</t>
+          <t>Carolyn Ang</t>
         </is>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>Lunate</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -11141,12 +11185,12 @@
     <row r="185" ht="14" customHeight="1">
       <c r="A185" s="10" t="inlineStr">
         <is>
-          <t>Changxian Beijing</t>
+          <t>Carsten Bachg</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>Ares Strategic Mining</t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
@@ -11173,12 +11217,12 @@
     <row r="186" ht="14" customHeight="1">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>Chantelle Collins</t>
+          <t>Changxian Beijing</t>
         </is>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Trident Resources</t>
+          <t>Ares Strategic Mining</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
@@ -11205,12 +11249,12 @@
     <row r="187" ht="14" customHeight="1">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>Charles Xuereb</t>
+          <t>Chantelle Collins</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>Trident Estates</t>
+          <t>Trident Resources</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
@@ -11237,12 +11281,12 @@
     <row r="188" ht="14" customHeight="1">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>Chen Qiuhai</t>
+          <t>Charles Xuereb</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Yamada Green Resources</t>
+          <t>Trident Estates</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
@@ -11252,7 +11296,7 @@
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
@@ -11269,12 +11313,12 @@
     <row r="189" ht="14" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>Chi Tung Liu</t>
+          <t>Chen Qiuhai</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>Novatek Microelectronics</t>
+          <t>Yamada Green Resources</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
@@ -11284,7 +11328,7 @@
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr">
@@ -11301,12 +11345,12 @@
     <row r="190" ht="14" customHeight="1">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>Chih-Hsien Lo</t>
+          <t>Chi Tung Liu</t>
         </is>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Prince Housing &amp; Development</t>
+          <t>Novatek Microelectronics</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
@@ -11316,7 +11360,7 @@
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
@@ -11333,12 +11377,12 @@
     <row r="191" ht="14" customHeight="1">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>Chris McGinnis</t>
+          <t>Chih-Hsien Lo</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>Playtech</t>
+          <t>Prince Housing &amp; Development</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
@@ -11348,7 +11392,7 @@
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr">
@@ -11365,22 +11409,22 @@
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>Christian Windfuhr</t>
+          <t>Chris McGinnis</t>
         </is>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Grand City Properties</t>
+          <t>Playtech</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
@@ -11397,22 +11441,22 @@
     <row r="193" ht="14" customHeight="1">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>Christopher Marshall</t>
+          <t>Christian Windfuhr</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>Payoneer</t>
+          <t>Grand City Properties</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
@@ -11429,12 +11473,12 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="10" t="inlineStr">
         <is>
-          <t>Christopher Moreno</t>
+          <t>Christopher Marshall</t>
         </is>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Energy Resources</t>
+          <t>Payoneer</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -11461,22 +11505,22 @@
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>Chye Guan</t>
+          <t>Christopher Moreno</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>Quantum Asset Management (Si</t>
+          <t>Vulcan Energy Resources</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Asset Manager</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr">
@@ -11493,17 +11537,17 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="10" t="inlineStr">
         <is>
-          <t>Clemens Gregor</t>
+          <t>Chye Guan</t>
         </is>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Finad Group</t>
+          <t>Quantum Asset Management (Si</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>Investor</t>
+          <t>Asset Manager</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
@@ -11525,22 +11569,22 @@
     <row r="197" ht="14" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>Craig Hewitt</t>
+          <t>Clemens Gregor</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Delta Seaboard Well Service </t>
+          <t>Finad Group</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>Investor</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
@@ -11557,12 +11601,12 @@
     <row r="198" ht="14" customHeight="1">
       <c r="A198" s="10" t="inlineStr">
         <is>
-          <t>D. Mark Appleby</t>
+          <t>Craig Hewitt</t>
         </is>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>Tartisan Nickel</t>
+          <t xml:space="preserve">Delta Seaboard Well Service </t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -11589,12 +11633,12 @@
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>Dana Codding</t>
+          <t>D. Mark Appleby</t>
         </is>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>Parkland</t>
+          <t>Tartisan Nickel</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -11621,12 +11665,12 @@
     <row r="200" ht="14" customHeight="1">
       <c r="A200" s="10" t="inlineStr">
         <is>
-          <t>Daniel Halyk</t>
+          <t>Dana Codding</t>
         </is>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>Total Energy Services</t>
+          <t>Parkland</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
@@ -11653,12 +11697,12 @@
     <row r="201" ht="14" customHeight="1">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>Daniel Major</t>
+          <t>Daniel Halyk</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>GoviEx Uranium</t>
+          <t>Total Energy Services</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
@@ -11685,12 +11729,12 @@
     <row r="202" ht="14" customHeight="1">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>Daniel Ninivaggi</t>
+          <t>Daniel Major</t>
         </is>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>Indivior</t>
+          <t>GoviEx Uranium</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
@@ -11717,12 +11761,12 @@
     <row r="203" ht="14" customHeight="1">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>Danny Callow</t>
+          <t>Daniel Ninivaggi</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>Toubani Resources</t>
+          <t>Indivior</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -11749,12 +11793,12 @@
     <row r="204" ht="14" customHeight="1">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>Darwin Green</t>
+          <t>Danny Callow</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>Contango ORE</t>
+          <t>Toubani Resources</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -11764,7 +11808,7 @@
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E204" s="12" t="inlineStr">
@@ -11905,15 +11949,15 @@
         <v>9</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1159.2</v>
+        <v>1501.1</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>258.1</v>
+        <v>408.9</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -11928,10 +11972,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1309.4</v>
+        <v>1184.1</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
@@ -11939,7 +11983,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>117.9</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -11954,18 +11998,18 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2792</v>
+        <v>3008.2</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>GOOGN</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>137</v>
+        <v>222.1</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -12006,18 +12050,18 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>19007.6</v>
+        <v>48245.6</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>372.5</v>
+        <v>1757.6</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>4.4</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>32.3</v>
+        <v>30.8</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>4.6</v>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>24.9</v>
+        <v>26.7</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1375,14 +1375,14 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications, In</t>
+          <t>Under Armour, Inc.</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
-        <v>20.3</v>
+        <v>25.7</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="E14" s="11" t="n">
         <v>1.9</v>
@@ -1457,7 +1457,7 @@
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>QXO, Inc.</t>
+          <t>Charter Communications, In</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7.1</v>
+        <v>4.7</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1496,14 +1496,14 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology, Inc.</t>
+          <t>QXO, Inc.</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>2.3</v>
+        <v>7.1</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Under Armour, Inc.</t>
+          <t>Sana Biotechnology, Inc.</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
-        <v>14.9</v>
+        <v>16.6</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>1</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="D22" s="11" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>2</v>
@@ -1871,7 +1871,7 @@
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Innoviva, Inc.</t>
+          <t>Agenus Inc.</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Agenus Inc.</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>1</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>1.5</v>
@@ -2883,7 +2883,7 @@
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2893,26 +2893,26 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>SLB N.V.</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>2011</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>19.6</v>
+        <v>18.9</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2985,26 +2985,26 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>SLB N.V.</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
         <v>18.7</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1</v>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>2011</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler,George Willis,Thomas Fanni</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="E53" s="11" t="n">
         <v>0.6</v>
@@ -3527,7 +3527,7 @@
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>NGVT</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -3537,14 +3537,14 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy, Inc.</t>
+          <t>Ingevity Corporation</t>
         </is>
       </c>
       <c r="D60" s="11" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>1</v>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Daniel Sansone</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3566,14 +3566,14 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>NGVT</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Ingevity Corporation</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>Daniel Sansone</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -3629,14 +3629,14 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Ring Energy, Inc.</t>
         </is>
       </c>
       <c r="D62" s="11" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>1</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -3757,7 +3757,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -3767,43 +3767,43 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holdi</t>
+          <t>Porch Group, Inc.</t>
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Amanda Reierson</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Porch Group, Inc.</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>1</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Amanda Reierson</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3849,7 +3849,7 @@
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3859,43 +3859,43 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3905,14 +3905,14 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
         <v>3.3</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
         <v>3.3</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>1</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4043,26 +4043,26 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -4089,26 +4089,26 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>Sprouts Farmers Market, In</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -4135,43 +4135,43 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, In</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>2003</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -4181,43 +4181,43 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -4227,43 +4227,43 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -4273,31 +4273,31 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>2005</t>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>United Microelectronics Co</t>
         </is>
       </c>
       <c r="D77" s="11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>1</v>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4348,14 +4348,14 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -4365,14 +4365,14 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics Co</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="D78" s="11" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>1</v>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4394,14 +4394,14 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
@@ -4411,26 +4411,26 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Trident Digital Tech Holdi</t>
         </is>
       </c>
       <c r="D79" s="11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>-5.2</v>
+        <v>-5.5</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>1</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>4.4</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>0.6</v>
@@ -5695,18 +5695,18 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>32.3</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Pamala Kaufman</t>
+          <t>Leonard Potter</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Lindblad Expeditions Holding</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -5721,82 +5721,82 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>HGV</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>29.4</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Viral Patel</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>Under Armour</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UAA</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Leonard Potter</t>
+          <t>Viral Patel</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>HGV</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Ashwini Kumar</t>
+          <t>Hope Woodhouse</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Monro</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -5811,22 +5811,22 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MNRO</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>Pamala Kaufman</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Lindblad Expeditions Holding</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -5841,22 +5841,22 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>20.3</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Ashok Srivastava</t>
+          <t>Ashwini Kumar</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -5871,22 +5871,22 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>20.1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Ashok Srivastava</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -5901,11 +5901,11 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -6265,18 +6265,18 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -6291,22 +6291,22 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
@@ -6331,12 +6331,12 @@
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -6351,22 +6351,22 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -6381,22 +6381,22 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>17.6</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -6411,22 +6411,22 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>17.6</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Hope Woodhouse</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Monro</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -6441,22 +6441,22 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>MNRO</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -6471,22 +6471,22 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -6501,22 +6501,22 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -6531,22 +6531,22 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>David Wright</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>Rezolve Ai</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -6556,27 +6556,27 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>RZLVW</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>David Wright</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Rezolve Ai</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -6586,27 +6586,27 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>RZLVW</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>15.6</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Richard Russell</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>LM Funding America</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>LMFA</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick</t>
+          <t>Richard Russell</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>LM Funding America</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -6651,11 +6651,11 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>UAA</t>
+          <t>LMFA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
@@ -7351,12 +7351,12 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Mohammad Abu-Ghazaleh</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Fresh Del Monte Produce</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -7366,27 +7366,27 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Mohammad Abu-Ghazaleh</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Fresh Del Monte Produce</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -7396,16 +7396,16 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -7621,12 +7621,12 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -7641,22 +7641,22 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
@@ -7711,12 +7711,12 @@
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Tim Cahill</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
@@ -7741,12 +7741,12 @@
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Tim Cahill</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -7761,22 +7761,22 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -7821,22 +7821,22 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
@@ -8011,12 +8011,12 @@
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Haiyan Huang</t>
+          <t>Hock Goh</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>SKF</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
@@ -8031,22 +8031,22 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>SKF-B.ST</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Poh Kiong Tan</t>
+          <t>Nicholas Zangler</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>Viant Technology</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
@@ -8061,22 +8061,22 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>DSP</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Soon Huat Lim</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Trident Digital Tech Holding</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>TDTH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Hock Goh</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>SKF</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -8121,22 +8121,22 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>SKF-B.ST</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Mon</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -8151,22 +8151,22 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>Aris Kekedjian</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>Stratasys (Printing Services</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
@@ -8181,22 +8181,22 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Commercial Metals</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
@@ -8211,22 +8211,22 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Nicholas Zangler</t>
+          <t>Phillip Kardis</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Viant Technology</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
@@ -8236,27 +8236,27 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>DSP</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>Subramaniam Viswanathan</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Chimera Investment</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
@@ -8266,27 +8266,27 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>CIM-PD</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Aris Kekedjian</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Stratasys (Printing Services</t>
+          <t>National Bank of Canada (Mon</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -8301,22 +8301,22 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Phillip Kardis</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -8326,27 +8326,27 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Subramaniam Viswanathan</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>Chimera Investment</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -8356,27 +8356,27 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>CIM-PD</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Richard Massey</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Jena Acquisition II</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
@@ -8391,22 +8391,22 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JENA-UN</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -8421,22 +8421,22 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -8451,22 +8451,22 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Richard Massey</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Jena Acquisition II</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>JENA-UN</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -8581,7 +8581,7 @@
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -8611,7 +8611,7 @@
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -8701,7 +8701,7 @@
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -8731,12 +8731,12 @@
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
@@ -8751,22 +8751,22 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
@@ -8781,22 +8781,22 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="109" ht="14" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
@@ -8811,22 +8811,22 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -8836,27 +8836,27 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -8871,22 +8871,22 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Jane O'Keeffe</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Bancroft Fund</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -8901,22 +8901,22 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>BCV-PA</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -8926,27 +8926,27 @@
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Chi-Tung Liu</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
@@ -8961,22 +8961,22 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="115" ht="14" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Jane O'Keeffe</t>
+          <t>Jason Wang</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>Bancroft Fund</t>
+          <t>United Microelectronics</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
@@ -8991,22 +8991,22 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>BCV-PA</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="116" ht="14" customHeight="1">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Vuyo Kahla</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Sasol</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
@@ -9016,27 +9016,27 @@
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>SASOF</t>
         </is>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>Chi-Tung Liu</t>
+          <t>Aviad Kaufman</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
@@ -9051,22 +9051,22 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F117" s="12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="118" ht="14" customHeight="1">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>Jason Wang</t>
+          <t>Idan Ofer</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>United Microelectronics</t>
+          <t>Kenon Holdings</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
@@ -9081,22 +9081,22 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="F118" s="12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>Vuyo Kahla</t>
+          <t>Massimo Belcredi</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>Sasol</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
@@ -9106,27 +9106,27 @@
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>SASOF</t>
+          <t>EIPAF</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="120" ht="14" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>Aviad Kaufman</t>
+          <t>Vincent Intrieri</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
@@ -9141,22 +9141,22 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>HTZ 8 07-15-29</t>
         </is>
       </c>
       <c r="F120" s="12" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="121" ht="14" customHeight="1">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>Idan Ofer</t>
+          <t>Haiyan Huang</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>Kenon Holdings</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
@@ -9171,22 +9171,22 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F121" s="12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" ht="14" customHeight="1">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>Massimo Belcredi</t>
+          <t>Poh Kiong Tan</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
@@ -9201,22 +9201,22 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>EIPAF</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F122" s="12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" ht="14" customHeight="1">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>Vincent Intrieri</t>
+          <t>Soon Huat Lim</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Trident Digital Tech Holding</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
@@ -9231,11 +9231,11 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>HTZ 8 07-15-29</t>
+          <t>TDTH</t>
         </is>
       </c>
       <c r="F123" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="F127" s="12" t="n">
-        <v>-5.2</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">

--- a/people_monitor.xlsx
+++ b/people_monitor.xlsx
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0.9</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>1</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="D16" s="11" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>1</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D18" s="11" t="n">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>1</v>
@@ -1917,7 +1917,7 @@
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Innoviva, Inc.</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -1946,24 +1946,24 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Sharmila Mulligan</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1973,14 +1973,14 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture plc</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -2002,14 +2002,14 @@
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -2019,14 +2019,14 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Lands' End, Inc.</t>
+          <t>DFS Furniture plc</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1</v>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Josephine Linden</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>PMTR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2065,11 +2065,11 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Perimeter Acquisition Corp</t>
+          <t>Lands' End, Inc.</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="E28" s="11" t="n">
         <v>1.9</v>
@@ -2084,24 +2084,24 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Jack Selby</t>
+          <t>Josephine Linden</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>PMTR</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -2111,14 +2111,14 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Perimeter Acquisition Corp</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>1</v>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>Sharmila Mulligan</t>
+          <t>Jack Selby</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2295,14 +2295,14 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Oklo Inc.</t>
+          <t>Star Bulk Carriers Corp.</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>1</v>
@@ -2314,24 +2314,24 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Samuel Altman</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>Titans &amp; Concentrated Ma</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -2341,14 +2341,14 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers Corp.</t>
+          <t>Oklo Inc.</t>
         </is>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2360,24 +2360,24 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Samuel Altman</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Titans &amp; Concentrated Ma</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>EVR</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Telefônica Brasil S.A.</t>
+          <t>Evercore Inc.</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
         <v>1.1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>1</v>
@@ -2406,24 +2406,24 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Jonathan Knee</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>EVR</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -2433,14 +2433,14 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Evercore Inc.</t>
+          <t>Telefônica Brasil S.A.</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>1</v>
@@ -2452,17 +2452,17 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Knee</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="D45" s="11" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>1.5</v>
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="D47" s="11" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>3</v>
@@ -2992,7 +2992,7 @@
         <v>18.7</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>1</v>
@@ -3021,7 +3021,7 @@
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings, Inc.</t>
+          <t>Xometry, Inc.</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>1</v>
@@ -3050,24 +3050,24 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Katharine Weymouth</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways plc</t>
+          <t>FRP Holdings, Inc.</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -3123,43 +3123,43 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Xometry, Inc.</t>
+          <t>VEON Ltd.</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2</v>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Katharine Weymouth</t>
+          <t>Brandon Lewis,Duncan Perry</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Se</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>DRIO</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -3169,43 +3169,43 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>VEON Ltd.</t>
+          <t>DarioHealth Corp.</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t>2023</t>
+        <v>1</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis,Duncan Perry</t>
+          <t>Yoav Shaked</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>Communication Se</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>DRIO</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>DarioHealth Corp.</t>
+          <t>Beazer Homes USA, Inc.</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
-        <v>17.4</v>
+        <v>16.1</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>1</v>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>Yoav Shaked</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclica</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA, Inc.</t>
+          <t>COMPASS Pathways plc</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>1</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclica</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="D57" s="11" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="E57" s="11" t="n">
         <v>2.5</v>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D61" s="11" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>1</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="D63" s="11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>1</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D65" s="11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1.3</v>
@@ -3803,7 +3803,7 @@
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>BSRR</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Sierra Bancorp</t>
+          <t>Guardant Health, Inc.</t>
         </is>
       </c>
       <c r="D66" s="11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>1</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>Laurence Dutto</t>
+          <t>Aaref Hilaly</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3842,14 +3842,14 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>CMC</t>
+          <t>BSRR</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3859,43 +3859,43 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Commercial Metals Company</t>
+          <t>Sierra Bancorp</t>
         </is>
       </c>
       <c r="D67" s="11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="F67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>2014</t>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>John McPherson</t>
+          <t>Laurence Dutto</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>CMC</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -3905,43 +3905,43 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Guardant Health, Inc.</t>
+          <t>Commercial Metals Company</t>
         </is>
       </c>
       <c r="D68" s="11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>2014</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>Aaref Hilaly</t>
+          <t>John McPherson</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies, Inc.</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="D69" s="11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>1</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Amprius Technologies, Inc.</t>
         </is>
       </c>
       <c r="D70" s="11" t="n">
         <v>3.3</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>1</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4043,26 +4043,26 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
+          <t>RELX PLC</t>
         </is>
       </c>
       <c r="D71" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -4089,26 +4089,26 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market, In</t>
+          <t>Harbour Energy plc</t>
         </is>
       </c>
       <c r="D72" s="11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>2018</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensi</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>UBSI</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
@@ -4135,43 +4135,43 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>United Bankshares, Inc.</t>
+          <t>Sprouts Farmers Market, In</t>
         </is>
       </c>
       <c r="D73" s="11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E73" s="11" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>2003</t>
+        <v>1</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>J. Mcnamara,Michael Fitzgerald</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
         <is>
-          <t>Sequoia Network</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>Financial Servic</t>
+          <t>Consumer Defensi</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>UBSI</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -4181,43 +4181,43 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group Ltd</t>
+          <t>United Bankshares, Inc.</t>
         </is>
       </c>
       <c r="D74" s="11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>J. Mcnamara,Michael Fitzgerald</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Sequoia Network</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Servic</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -4227,43 +4227,43 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Danaos Corporation</t>
+          <t>Woodside Energy Group Ltd</t>
         </is>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Office</t>
+          <t>Billionaire/Oligarch Veh</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -4273,31 +4273,31 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>RELX PLC</t>
+          <t>Danaos Corporation</t>
         </is>
       </c>
       <c r="D76" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E76" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="E76" s="11" t="n">
-        <v>0.6</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>2005</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch Veh</t>
+          <t>Gulf/Royal Family Office</t>
         </is>
       </c>
       <c r="J76" s="10" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="D80" s="11" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="F80" s="12" t="n">
         <v>1</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>0.9</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="F5" s="12" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -5905,18 +5905,18 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Gregory Landis</t>
+          <t>Andrew Crowley</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>H2O America</t>
+          <t>Markel Group</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>MKL</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>C. Wes Burton</t>
+          <t>Gregory Landis</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Vulcan Materials</t>
+          <t>H2O America</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5961,17 +5961,17 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Cynthia Hostetler</t>
+          <t>C. Wes Burton</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>David Clement</t>
+          <t>Cynthia Hostetler</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Denson Franklin</t>
+          <t>David Clement</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>George Willis</t>
+          <t>Denson Franklin</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>J. Hill</t>
+          <t>George Willis</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -6115,13 +6115,13 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>J. Thomas Hill</t>
+          <t>J. Hill</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -6145,13 +6145,13 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Jerry Perkins</t>
+          <t>J. Thomas Hill</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Mark Warren</t>
+          <t>Jerry Perkins</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -6205,13 +6205,13 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Mary Carlisle</t>
+          <t>Mark Warren</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Thomas Fanning</t>
+          <t>Mary Carlisle</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -6265,18 +6265,18 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Tatiana Mitrova</t>
+          <t>Thomas Fanning</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>SLB (Other Energy Services</t>
+          <t>Vulcan Materials</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -6291,22 +6291,22 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>John Baker</t>
+          <t>Tatiana Mitrova</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>FRP Holdings</t>
+          <t>SLB (Other Energy Services</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -6321,22 +6321,22 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>FRPH</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Annalisa Jenkins</t>
+          <t>W. Conn</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>COMPASS Pathways</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -6351,22 +6351,22 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>W. Conn</t>
+          <t>John Baker</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>FRP Holdings</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -6381,22 +6381,22 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FRPH</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Andrew Crowley</t>
+          <t>Brandon Lewis</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Markel Group</t>
+          <t>Veon</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -6411,17 +6411,17 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>MKL</t>
+          <t>VEON</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Brandon Lewis</t>
+          <t>Duncan Perry</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -6451,12 +6451,12 @@
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Duncan Perry</t>
+          <t>Mary Kissel</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Veon</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -6471,22 +6471,22 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>VEON</t>
+          <t>QXO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>17.6</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Mary Kissel</t>
+          <t>Richard Mulligan</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>Sana Biotechnology</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -6501,22 +6501,22 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>QXO</t>
+          <t>SANA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Richard Mulligan</t>
+          <t>David Wright</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Sana Biotechnology</t>
+          <t>Rezolve Ai</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -6526,27 +6526,27 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>SANA</t>
+          <t>RZLVW</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>David Wright</t>
+          <t>Danny Shepherd</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Rezolve Ai</t>
+          <t>Beazer Homes USA</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>RZLVW</t>
+          <t>BZH</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
@@ -6571,12 +6571,12 @@
     <row r="35" ht="14" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Danny Shepherd</t>
+          <t>Michael Insulan</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Beazer Homes USA</t>
+          <t>Electra Battery Materials</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -6591,22 +6591,22 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>BZH</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Michael Insulan</t>
+          <t>Derek Kan</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Electra Battery Materials</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6621,11 +6621,11 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
@@ -6661,12 +6661,12 @@
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Derek Kan</t>
+          <t>James Nelson</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Global Net Lease</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -6681,22 +6681,22 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>TOL</t>
+          <t>GNL</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>James Nelson</t>
+          <t>Annalisa Jenkins</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Global Net Lease</t>
+          <t>COMPASS Pathways</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -6711,22 +6711,22 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>GNL</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Christodoro</t>
+          <t>Joseph Flaim</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Iamgold</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -6736,27 +6736,27 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>Louis Pastor</t>
+          <t>Franz Humer</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Xerox</t>
+          <t>Allogene Therapeutics</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -6771,22 +6771,22 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>ALLO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Joseph Flaim</t>
+          <t>Meryl Hartzband</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Iamgold</t>
+          <t>Everest Group (Hamilton</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -6796,27 +6796,27 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>Franz Humer</t>
+          <t>Wilbur Ross</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Allogene Therapeutics</t>
+          <t>Coya Therapeutics</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>ALLO</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Meryl Hartzband</t>
+          <t>Jonathan Frates</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Everest Group (Hamilton</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6861,22 +6861,22 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>13</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>Wilbur Ross</t>
+          <t>Nancy Dunlap</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Coya Therapeutics</t>
+          <t>SandRidge Energy</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -6891,22 +6891,22 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Jonathan Frates</t>
+          <t>Bill Roeschlein</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Tigo Energy</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6921,22 +6921,22 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TYGO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>12.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Nancy Dunlap</t>
+          <t>Kathleen Quirk</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>SandRidge Energy</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6951,22 +6951,22 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Bill Roeschlein</t>
+          <t>Wendy Teramoto</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Tigo Energy</t>
+          <t>The Greenbrier Companies</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -6981,22 +6981,22 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>TYGO</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Wendy Teramoto</t>
+          <t>Anthony Williams</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>The Greenbrier Companies</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>Thierry Pilenko</t>
+          <t>Kelly Osborne</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>LanzaTech Global</t>
+          <t>Kinross Gold</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>KGCRF</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
@@ -7051,12 +7051,12 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Kelly Osborne</t>
+          <t>Thierry Pilenko</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Kinross Gold</t>
+          <t>LanzaTech Global</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>KGCRF</t>
+          <t>LNZA</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
@@ -7081,12 +7081,12 @@
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Kathleen Quirk</t>
+          <t>Sandra Bell</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Dye &amp; Durham</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>DYNDF</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
@@ -7111,12 +7111,12 @@
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>Sandra Bell</t>
+          <t>Stephen Gunther</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Dye &amp; Durham</t>
+          <t>Shoulder Innovations</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -7131,22 +7131,22 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>DYNDF</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Stephen Gunther</t>
+          <t>Kenneth Gunderman</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Shoulder Innovations</t>
+          <t>Uniti Group (Financial Servi</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
@@ -7171,12 +7171,12 @@
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Kenneth Gunderman</t>
+          <t>Bryan Murphy</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Uniti Group (Financial Servi</t>
+          <t>Greenlight Capital Re</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -7191,22 +7191,22 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>GLRE</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Bryan Murphy</t>
+          <t>Allan D. Schoening</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Greenlight Capital Re</t>
+          <t>Civeo</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>GLRE</t>
+          <t>CVEO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Anthony Williams</t>
+          <t>Jeffrey Fox</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Westrock Coffee</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -7251,52 +7251,52 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Allan D. Schoening</t>
+          <t>Dominic Picone</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Civeo</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Public Company</t>
+          <t>PE/Buyout</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>CVEO</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Jeffrey Fox</t>
+          <t>Brian Corvese</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Westrock Coffee</t>
+          <t>Agenus</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -7311,27 +7311,27 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Dominic Picone</t>
+          <t>Mohammad Abu-Ghazaleh</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>Fresh Del Monte Produce</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>PE/Buyout</t>
+          <t>Public Company</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>FDP</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Brian Corvese</t>
+          <t>Jonathan Christodoro</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Agenus</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -7371,22 +7371,22 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Mohammad Abu-Ghazaleh</t>
+          <t>Louis Pastor</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Fresh Del Monte Produce</t>
+          <t>Xerox</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -7396,16 +7396,16 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>FDP</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
@@ -7501,12 +7501,12 @@
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Randle Reece</t>
+          <t>Sylvia Summers</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>AMN Healthcare Services</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -7521,22 +7521,22 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Pam Kaufman</t>
+          <t>Randle Reece</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Paramount Skydance</t>
+          <t>AMN Healthcare Services</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -7551,22 +7551,22 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>AMN</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Mark DiPaolo</t>
+          <t>Pam Kaufman</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Innoviva</t>
+          <t>Paramount Skydance</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7581,22 +7581,22 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>INVA</t>
+          <t>PSKY</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Sylvia Summers</t>
+          <t>David Allen</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -7611,22 +7611,22 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>David Habachy</t>
+          <t>Mark DiPaolo</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Ring Energy</t>
+          <t>Innoviva</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -7641,22 +7641,22 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>REI</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>David Moradi</t>
+          <t>David Habachy</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>AudioEye</t>
+          <t>Ring Energy</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -7671,22 +7671,22 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>REI</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Tiago Miranda</t>
+          <t>David Moradi</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>Atlas Lithium</t>
+          <t>AudioEye</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -7701,22 +7701,22 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>David Allen</t>
+          <t>Randall Weisenburger</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>MP Materials</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -7731,11 +7731,11 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
@@ -7765,18 +7765,18 @@
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Charles Leykum</t>
+          <t>Tiago Miranda</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Talon Capital (SPAC</t>
+          <t>Atlas Lithium</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>TLNC</t>
+          <t>ATLX</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Tony Buffin</t>
+          <t>Charles Leykum</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>DFS Furniture</t>
+          <t>Talon Capital (SPAC</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -7821,22 +7821,22 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>DFS.L</t>
+          <t>TLNC</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Randall Weisenburger</t>
+          <t>Tony Buffin</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>MP Materials</t>
+          <t>DFS Furniture</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>DFS.L</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
@@ -7921,12 +7921,12 @@
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Laura Duda</t>
+          <t>Oscar Iglesias</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber</t>
+          <t>Codere Online Luxembourg</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>CDROW</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
@@ -7951,12 +7951,12 @@
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Oscar Iglesias</t>
+          <t>Laura Duda</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Codere Online Luxembourg</t>
+          <t>The Goodyear Tire &amp; Rubber</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>CDROW</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
@@ -8065,18 +8065,18 @@
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>R. Cox</t>
+          <t>Rebecca Grossman-Cohen</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYT</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>John Campbell</t>
+          <t>R. Cox</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>Porch Group</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
@@ -8121,22 +8121,22 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Rebecca Grossman-Cohen</t>
+          <t>John Campbell</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Porch Group</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
@@ -8151,11 +8151,11 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>NYT</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
@@ -8281,12 +8281,12 @@
     <row r="92" ht="14" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Michael Denham</t>
+          <t>Anelise Lara</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>National Bank of Canada (Mon</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
@@ -8301,22 +8301,22 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Donald Dixon</t>
+          <t>Michael Denham</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Amprius Technologies</t>
+          <t>National Bank of Canada (Mon</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
@@ -8331,22 +8331,22 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Anelise Lara</t>
+          <t>Donald Dixon</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Amprius Technologies</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
@@ -8401,12 +8401,12 @@
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Michael Dougherty</t>
+          <t>Chris Siu</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>Polaris (Automotive</t>
+          <t>Aehr Test Systems</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
@@ -8421,22 +8421,22 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Chris Siu</t>
+          <t>Michael Dougherty</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Aehr Test Systems</t>
+          <t>Polaris (Automotive</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
@@ -8451,22 +8451,22 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Alan Ferguson</t>
+          <t>Suzanne Wood</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>Harbour Energy</t>
+          <t>RELX (Information Technology</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>RLXXF</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
@@ -8491,7 +8491,7 @@
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Alexander Krane</t>
+          <t>Alan Ferguson</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -8521,7 +8521,7 @@
     <row r="100" ht="14" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Andrea Pinarel</t>
+          <t>Alexander Krane</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -8551,7 +8551,7 @@
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>David Kennedy</t>
+          <t>Andrea Pinarel</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -8581,7 +8581,7 @@
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Feyyaz Etiz</t>
+          <t>David Kennedy</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -8611,7 +8611,7 @@
     <row r="103" ht="14" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Gustavo Baquero</t>
+          <t>Feyyaz Etiz</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Linda Cook</t>
+          <t>Gustavo Baquero</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Michael Tuffin</t>
+          <t>Linda Cook</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
@@ -8701,7 +8701,7 @@
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Nathan Mauzy</t>
+          <t>Michael Tuffin</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -8731,12 +8731,12 @@
     <row r="107" ht="14" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Raffaele Zagari</t>
+          <t>Nathan Mauzy</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Star Bulk Carriers</t>
+          <t>Harbour Energy</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
@@ -8751,22 +8751,22 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Douglas Rauch</t>
+          <t>Raffaele Zagari</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Star Bulk Carriers</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>SFM</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="F108" s="12" t="n">
@@ -8791,12 +8791,12 @@
     <row r="109" ht="14" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Arnaud Breuillac</t>
+          <t>Douglas Rauch</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Woodside Energy Group</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
@@ -8811,22 +8811,22 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>WOPEF</t>
+          <t>SFM</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Dimitris Vastarouchas</t>
+          <t>Arnaud Breuillac</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>Danaos</t>
+          <t>Woodside Energy Group</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
@@ -8836,27 +8836,27 @@
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Gulf/Royal Family Offi</t>
+          <t>Billionaire/Oligarch V</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>WOPEF</t>
         </is>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Peter Loscher</t>
+          <t>Dimitris Vastarouchas</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>Telefónica</t>
+          <t>Danaos</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
@@ -8866,27 +8866,27 @@
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Billionaire/Oligarch V</t>
+          <t>Gulf/Royal Family Offi</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>VIV</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Jane O'Keeffe</t>
+          <t>Peter Loscher</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>Bancroft Fund</t>
+          <t>Telefónica</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>BCV-PA</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="F112" s="12" t="n">
@@ -8911,12 +8911,12 @@
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>Suzanne Wood</t>
+          <t>Jane O'Keeffe</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>RELX (Information Technology</t>
+          <t>Bancroft Fund</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
@@ -8931,11 +8931,11 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>RLXXF</t>
+          <t>BCV-PA</t>
         </is>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="F125" s="12" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="126" ht="14" customHeight="1">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="F127" s="12" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
